--- a/extraction/stec.xlsx
+++ b/extraction/stec.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,25 +439,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Gibson Dunn</t>
+          <t>Gibson, Dunn &amp; Crutcher LLP</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -614,15 +614,19 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Target legal adviser: engaged October 2012 as sTec's outside corporate counsel; advised the board and special committee on fiduciary duties and negotiated the merger agreement with WDC's counsel (Shearman).</t>
+          <t>Target’s outside corporate (legal) counsel, engaged October 2012; advised the board and special committee on fiduciary duties and negotiated the merger agreement with WDC’s counsel.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“a representative from the law firm of Gibson, Dunn &amp; Crutcher LLP (“Gibson Dunn”), which had been engaged in October 2012 as the company’s outside corporate counsel” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="n"/>
+          <t>“which had been engaged in October 2012 as the company’s outside corporate counsel” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="3" t="n">
         <v>41198</v>
@@ -676,7 +680,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>First contact, inbound via Company A's investment bank; draft NDA for evaluating a possible business transaction; scheduled meeting cancelled after non-management directors' concerns about A management's involvement. No NDA. Later among nine that said not interested in BofA outreach (p. 27).</t>
+          <t>First contact, bidder-initiated via Company A’s (unnamed) investment bank; no price. Bank sent agenda and draft NDA for “a possible business transaction”. Scheduled meeting later cancelled (undated) over non-management directors’ concerns; no NDA signed. Company A later told BofA it was not interested (p. 27).</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -736,7 +740,7 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Board decided to undertake a formal review of strategic alternatives, including a potential sale, as a market check against standalone cost cuts; authorized management to contact financial advisers. Two advisers contacted declined; none engaged; review continued.</t>
+          <t>Board, weighing cost cuts, decided to undertake a formal review of strategic alternatives including a potential sale (a market check versus standalone), and authorized management to contact financial advisers. Two advisers contacted declined; none engaged; board continued the review.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -771,7 +775,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Balch Hill</t>
+          <t>Balch Hill Partners, L.P.</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -796,7 +800,7 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Activist Balch Hill Partners filed first Schedule 13D (6.4% stake). Later joined by Potomac Capital Partners II (jointly 9.8%); campaign, including nomination of three directors for the 2013 annual meeting, continued until the merger announcement.</t>
+          <t>Activist Balch Hill filed its first Schedule 13D, reporting 6.4%; later joined by Potomac Capital Partners II (together 9.8%). Campaign continued until the merger announcement and included nominating three directors for the 2013 annual meeting.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -804,7 +808,11 @@
           <t>“Balch Hill filed its first Schedule 13D with the SEC on November 16, 2012.” (p. 25)</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="3" t="n">
         <v>41229</v>
@@ -827,7 +835,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Balch Hill</t>
+          <t>Balch Hill Partners, L.P.</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -852,15 +860,19 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Balch Hill amended its 13D and wrote to the board urging cost cuts, a focus on SAS-interface products and exploration of strategic alternatives; also advocated reversing sTec's new go-to-market strategy.</t>
+          <t>Balch Hill amended its 13D and wrote to the board urging cost cuts, a focus on SAS-interface products and exploration of strategic alternatives; it and Potomac advocated reversing sTec’s new go-to-market strategy.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“issued a letter to our board of directors urging our board to reduce costs, focus on products with a SAS interface, and explore strategic alternatives.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="n"/>
+          <t>“on December 6, 2012, Balch Hill filed an amendment to its Schedule 13D, and concurrently issued a letter to our board of directors urging our board to reduce costs” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
         <v>41249</v>
@@ -908,7 +920,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Board formed a special committee (Daly, Colpitts, Witte; Bahri added 03/26) to review strategic alternatives, including a possible sale or standalone with further cost cuts; authorized to engage advisers. Independent directors to handle activist responses. Banker search of nine firms began 02/14.</t>
+          <t>Board formed a special committee of independent directors (Daly, Colpitts, Witte; Bahri added 03/26/2013) to review strategic alternatives including a sale versus standalone cost cuts, authorized to engage a financial adviser. Nine banks then canvassed; three interviewed late February.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -916,11 +928,7 @@
           <t>“The mandate of the special committee was to conduct a review of sTec’s strategic alternatives, including a possible sale of the company” (p. 25)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
         <v>41318</v>
@@ -974,17 +982,17 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>First contact, at a meeting with M. Moshayedi: B's President planned to present sTec to B management as a target. sTec sent a business presentation (no NDA reported). About two weeks later B declined; it would develop the technology itself.</t>
+          <t>First contact: Company B’s President (electronics industry) told Manouch Moshayedi he would present sTec to B’s management as a possible acquisition target; no price. sTec then forwarded B a presentation on its technology and business (undated). No NDA reported.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“the President intended to present sTec as a possible acquisition target to the management of Company B.” (p. 25)</t>
+          <t>“the President intended to present sTec as a possible acquisition target to the management of Company B” (p. 25)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S8" s="2" t="n"/>
@@ -1004,12 +1012,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>03/13/2013</t>
+          <t>about two weeks after sTec sent Company B a presentation (after 02/13/2013)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Company C</t>
+          <t>Company B</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1019,7 +1027,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1040,12 +1048,12 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Inbound, within an existing business relationship: C was interested in particular assets and considering a proposal. On 04/15 it said it wanted only select assets, and the committee ended talks (p. 28). No NDA. Assumed one of the 18 (#13).</t>
+          <t>Company B declines: its executive management was not interested in acquiring sTec and could develop the needed technology internally. Company B never entered (no NDA or bid), so no exit label. Sort date set about two weeks after the earliest possible forwarding date.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“the representatives of Company C, among other matters, expressed a potential interest in exploring an acquisition of particular assets of sTec’s business.” (p. 26)</t>
+          <t>“Company B’s management had determined that it was not interested in acquiring sTec and believed that it could independently develop the technology it needed to compete in enterprise SSDs” (p. 26)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1055,14 +1063,12 @@
       </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>41346</v>
+        <v>41332</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>41346</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>41346</v>
-      </c>
+        <v>41318</v>
+      </c>
+      <c r="V9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1070,12 +1076,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mid-March 2013</t>
+          <t>03/13/2013</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>Company C</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1085,7 +1091,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1106,24 +1112,28 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>First contact, inbound: D's head of corporate development (storage industry) approached management; management met D at special committee direction; D sent a draft NDA on 03/26. D is one of the 18 parties in the BofA total (#13).</t>
+          <t>Bidder-initiated contact during an ordinary business meeting: Company C (semiconductor industry) expressed potential interest in acquiring particular assets of sTec and said it was considering submitting an acquisition proposal. No price; no NDA reported.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“the head of corporate development for Company D, a participant in the storage industry, contacted our management to express the interest of Company D in exploring a potential acquisition” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
+          <t>“the representatives of Company C, among other matters, expressed a potential interest in exploring an acquisition of particular assets of sTec’s business” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>41348</v>
+        <v>41346</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>41344</v>
+        <v>41346</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>41352</v>
+        <v>41346</v>
       </c>
     </row>
     <row r="11">
@@ -1132,18 +1142,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/26/2013</t>
+          <t>mid-March 2013</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1162,24 +1176,24 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Board decided to approach confidentially the strategic buyers most likely to be interested, with only a limited confirmatory check of financial buyers (seen as uninterested and constrained on debt financing); directed that BofA be told this approach.</t>
+          <t>First contact, bidder-initiated: Company D’s head of corporate development contacted management about acquiring sTec; no price. Management met D at the special committee’s direction; D sent a draft NDA on 03/26/2013.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“our board of directors determined that it was in the best interests of the company and its shareholders to confidentially approach strategic buyers” (p. 27)</t>
+          <t>“Company D, a participant in the storage industry, contacted our management to express the interest of Company D in exploring a potential acquisition of the company” (p. 27)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>41359</v>
+        <v>41348</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>41359</v>
+        <v>41344</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>41359</v>
+        <v>41352</v>
       </c>
     </row>
     <row r="12">
@@ -1218,7 +1232,7 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target's sole financial adviser: board approved retention on special committee recommendation; engagement letter 03/28. Fee about $4.3 million, mostly contingent on completion. BofA had banking relationships with WDC, about $45 million revenue 2011–mid-2013 (p. 44).</t>
+          <t>Target’s financial adviser. Board approved retention on the special committee’s recommendation for the strategic review and defensive preparedness; engagement letter signed 03/28/2013. Delivered the 06/23/2013 fairness opinion.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1226,7 +1240,11 @@
           <t>“the board approved retaining BofA Merrill Lynch to act as sTec’s financial advisor in connection with the company’s general review of strategic alternatives and defensive preparedness” (p. 27)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
         <v>41359</v>
@@ -1244,7 +1262,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>04/01/2013</t>
+          <t>03/26/2013</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1255,14 +1273,14 @@
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
@@ -1274,12 +1292,12 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>BofA began contacting potential acquirers from a list set with management, at special committee direction. Data room populated from early April. Management presentations weeks of 04/08–04/22 to WDC, D, G and E; F declined one.</t>
+          <t>Board decided to confidentially approach the strategic buyers most likely to be interested and to conduct a limited confirmatory exploration of financial buyers (noting their lack of interest and debt-financing difficulty); directed BofA accordingly.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“On April 1, 2013, as directed by the special committee, BofA Merrill Lynch began contacting potential acquirers of sTec.” (p. 27)</t>
+          <t>“to confidentially approach strategic buyers that the board believed would be most likely to have interest in a potential acquisition of the company to explore their interest” (p. 27)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -1289,13 +1307,13 @@
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>41365</v>
+        <v>41359</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>41365</v>
+        <v>41359</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>41365</v>
+        <v>41359</v>
       </c>
     </row>
     <row r="14">
@@ -1304,22 +1322,18 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>from 04/01/2013</t>
+          <t>04/01/2013</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13 strategic prospective acquirers (incl. WDC, Companies E, F, G)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1333,24 +1347,22 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>BofA spoke with 18: 17 technology companies, 1 sponsor. Residual 13 = 18 less A (#2), C (#8), D (#9), H (#24) and the sponsor (#14). Outcome: WDC, D, H bid; six (incl. C, E, F) wanted only assets; nine (incl. A, sponsor) not interested.</t>
+          <t>Round 1 opens with BofA’s outreach wave to a list agreed with management; no due date at opening. Virtual data room populated from early April; management presentations to WDC, D, G and E during weeks of 04/08–04/22.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“In total, BofA Merrill Lynch had discussions with 18 prospective acquirers, 17 of which were technology companies and one of which was a financial sponsor.” (p. 27)</t>
+          <t>“On April 1, 2013, as directed by the special committee, BofA Merrill Lynch began contacting potential acquirers of sTec.” (p. 27)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
@@ -1360,7 +1372,9 @@
       <c r="U14" s="3" t="n">
         <v>41365</v>
       </c>
-      <c r="V14" s="2" t="n"/>
+      <c r="V14" s="3" t="n">
+        <v>41365</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1404,7 +1418,7 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>The only financial buyer in the BofA outreach, per the board's limited confirmatory check of financial buyers (#10); said it was not interested. Contact date not stated; outreach began 04/01.</t>
+          <t>Target-initiated contact by BofA; the only financial sponsor among the 18 prospective acquirers BofA spoke with. It indicated it was not interested; never entered.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1432,12 +1446,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/04/2013</t>
+          <t>from 04/01/2013</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Technology companies contacted by BofA (remainder of 17)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1447,7 +1461,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1461,32 +1475,32 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA includes a “don't ask, don't waive” standstill term surviving signing. First of six NDAs the filing counts for the sale exploration (E, D, F, G, WDC addendum, H).</t>
+          <t>Count: 12–14. Target-initiated BofA contacts. Filing total 18 (17 technology companies, 1 sponsor); A, D, H and the sponsor have own rows; B and C may be among the 17. Includes WDC. Outcomes of all 18: 3 whole-company IOIs (WDC, H, D), 6 asset-only interests, 9 not interested.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“On April 4, 2013, sTec entered into a non-disclosure agreement with Company E, a participant in the storage industry” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="n"/>
+          <t>“In total, BofA Merrill Lynch had discussions with 18 prospective acquirers, 17 of which were technology companies and one of which was a financial sponsor.” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>41368</v>
+        <v>41365</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>41368</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>41368</v>
-      </c>
+        <v>41365</v>
+      </c>
+      <c r="V16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1494,12 +1508,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/10/2013</t>
+          <t>04/04/2013</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1530,24 +1544,24 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA has no surviving “don't ask, don't waive” term.</t>
+          <t>Entry. NDA includes a “don’t ask, don’t waive” standstill that survives signing. One of six NDAs executed for the sale. Management presentation held during weeks of 04/08–04/22.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“on April 10, it entered into a non-disclosure agreement with Company D” (p. 27)</t>
+          <t>“On April 4, 2013, sTec entered into a non-disclosure agreement with Company E, a participant in the storage industry” (p. 27)</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>41374</v>
+        <v>41368</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>41374</v>
+        <v>41368</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>41374</v>
+        <v>41368</v>
       </c>
     </row>
     <row r="18">
@@ -1556,12 +1570,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>04/10/2013</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Company F</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1592,24 +1606,24 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Entry. Storage-industry participant; NDA includes a “don't ask, don't waive” standstill term surviving signing.</t>
+          <t>Entry. NDA (no surviving “don’t ask, don’t waive” term). Management presentation held during weeks of 04/08–04/22; follow-up diligence weeks of 04/22 and 04/29.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“on April 11, it entered into a non-disclosure agreement with Company F” (p. 27)</t>
+          <t>“on April 10, it entered into a non-disclosure agreement with Company D” (p. 27)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>41375</v>
+        <v>41374</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>41375</v>
+        <v>41374</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>41375</v>
+        <v>41374</v>
       </c>
     </row>
     <row r="19">
@@ -1618,12 +1632,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>04/17/2013</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
+          <t>Company F</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1654,24 +1668,24 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA has no surviving “don't ask, don't waive” term.</t>
+          <t>Entry. NDA includes a “don’t ask, don’t waive” standstill that survives signing.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“on April 17, it entered into a non-disclosure agreement with Company G, a participant in the storage industry” (p. 28)</t>
+          <t>“on April 11, it entered into a non-disclosure agreement with Company F” (p. 27)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>41381</v>
+        <v>41375</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>41381</v>
+        <v>41375</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>41381</v>
+        <v>41375</v>
       </c>
     </row>
     <row r="20">
@@ -1680,22 +1694,18 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>04/17/2013</t>
+          <t>04/15/2013</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1709,31 +1719,33 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Entry. Addendum (“special addendum”) to the existing WDC–sTec mutual NDA dated 01/29/2009 (p. 70); the row records its application to this process on 04/17/2013, not original execution. Management presentation to WDC 04/18.</t>
+          <t>Target ends discussions with Company C after C said it wanted only limited, select assets (scope, not a whole-company bid). C never entered, so no exit row.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“Also on April 17, 2013, sTec entered into an addendum to its existing non-disclosure agreement with WDC.” (p. 28)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>“it was only interested in purchasing limited, select assets of the company, and as a result, the special committee decided not to continue discussions with Company C” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>41381</v>
+        <v>41379</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41381</v>
+        <v>41379</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41381</v>
+        <v>41379</v>
       </c>
     </row>
     <row r="21">
@@ -1742,18 +1754,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>04/23/2013</t>
+          <t>04/17/2013</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t>Company G</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1767,29 +1783,31 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Process letters to WDC and Company D requested non-binding indications of interest due 05/03/2013. Company G received the same due date on 04/26 (#23).</t>
+          <t>Entry. NDA (no surviving “don’t ask, don’t waive” term). Management presentation during weeks of 04/08–04/22; follow-up diligence weeks of 04/22 and 04/29.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch sent process letters to WDC and Company D requesting non-binding indications of interest by May 3, 2013.” (p. 28)</t>
+          <t>“on April 17, it entered into a non-disclosure agreement with Company G, a participant in the storage industry” (p. 28)</t>
         </is>
       </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
     </row>
     <row r="22">
@@ -1798,12 +1816,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/23/2013</t>
+          <t>04/17/2013</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1813,7 +1831,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1822,25 +1840,11 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>5.6</v>
-      </c>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n">
         <v>1</v>
       </c>
@@ -1848,24 +1852,24 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>D detailed additional diligence requirements before a written indication; the committee had confidentiality concerns about them. Oral indication on a call with management and BofA; floor price “greater than $5.60” (Price low only).</t>
+          <t>Entry. Addendum to an existing WDC NDA (original date not stated), counted among six sale NDAs. WDC contacted in BofA outreach (in the 18). Management presentation 04/18/2013; follow-up diligence weeks of 04/22 and 04/29.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Company D provided a verbal indication of its interest to pursue a transaction at a price greater than $5.60 per share” (p. 28)</t>
+          <t>“Also on April 17, 2013, sTec entered into an addendum to its existing non-disclosure agreement with WDC.” (p. 28)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>41387</v>
+        <v>41381</v>
       </c>
     </row>
     <row r="23">
@@ -1874,22 +1878,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/24/2013</t>
+          <t>04/23/2013</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Company F</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1903,35 +1903,29 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>F declined to schedule a management presentation, saying it wanted only limited, select assets; no further communication with BofA or sTec. Bidder's decision.</t>
+          <t>Process letters to WDC and Company D request non-binding indications of interest by 05/03/2013. Company G got the same request 04/26/2013; E, F and H received none.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“on April 24, Company F declined the invitation to schedule a management presentation, indicating it was only interested in purchasing limited, select assets of sTec” (p. 28)</t>
+          <t>“BofA Merrill Lynch sent process letters to WDC and Company D requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>41388</v>
+        <v>41387</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>41388</v>
+        <v>41387</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>41388</v>
+        <v>41387</v>
       </c>
     </row>
     <row r="24">
@@ -1940,18 +1934,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>04/26/2013</t>
+          <t>04/23/2013</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1960,34 +1958,50 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="4" t="n">
+        <v>5.6</v>
+      </c>
       <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Process letter to Company G, at the chairman's direction for the special committee, requested a non-binding indication of interest by 05/03/2013 (same due date as #20).</t>
+          <t>Heavy: D detailed additional diligence requirements before any written indication. Verbal; price “greater than $5.60” (lower bound only). Consideration form not stated. Board later discussed confidentiality concerns about D’s diligence requests (04/25).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch sent a process letter to Company G requesting a non-binding indication of interest by May 3, 2013.” (p. 28)</t>
+          <t>“Company D provided a verbal indication of its interest to pursue a transaction at a price greater than $5.60 per share” (p. 28)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>41390</v>
+        <v>41387</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>41390</v>
+        <v>41387</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>41390</v>
+        <v>41387</v>
       </c>
     </row>
     <row r="25">
@@ -1996,12 +2010,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>05/01/2013</t>
+          <t>04/24/2013</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company F</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2011,7 +2025,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2028,28 +2042,32 @@
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>First contact, inbound to BofA (storage-industry participant, after outreach began); BofA sent H an NDA on 05/02 at the chairman's direction. One of the 18 (#13).</t>
+          <t>F declined a management presentation, saying it wanted only limited, select assets; no further communication with BofA or sTec.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“On May 1, 2013, Company H contacted representatives of BofA Merrill Lynch expressing an interest in a potential transaction with sTec.” (p. 29)</t>
+          <t>“on April 24, Company F declined the invitation to schedule a management presentation, indicating it was only interested in purchasing limited, select assets of sTec” (p. 28)</t>
         </is>
       </c>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>41395</v>
+        <v>41388</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>41395</v>
+        <v>41388</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>41395</v>
+        <v>41388</v>
       </c>
     </row>
     <row r="26">
@@ -2058,12 +2076,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>shortly after 04/24/2013</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2073,7 +2091,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2082,53 +2100,39 @@
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: management presentation 04/18; no data room until 05/10. Written indication of interest, range $6.60–$7.10 cash.</t>
+          <t>E said it wanted only limited, select assets; the special committee decided not to continue discussions. E was not among parties given follow-up diligence (weeks of 04/22 and 04/29) or process letters.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“On May 3, 2013, WDC submitted a written indication of interest to acquire the company at a purchase price in the range of $6.60 – $7.10 per share in cash.” (p. 29)</t>
+          <t>“Company E indicated it was also only interested in purchasing limited, select assets of sTec, and as a result the special committee decided not to continue discussions with Company E” (p. 28)</t>
         </is>
       </c>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>41397</v>
+        <v>41388</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>41397</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>41397</v>
-      </c>
+        <v>41388</v>
+      </c>
+      <c r="V26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2136,22 +2140,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>04/26/2013</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2165,35 +2165,29 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>G said it would not continue, on the indication due date; no reason given. Bidder's decision.</t>
+          <t>Process letter to Company G, sent at the chairman’s direction for the special committee, requests a non-binding indication of interest by the same 05/03/2013 date.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Also on May 3, 2013, Company G indicated it would not continue in the process.” (p. 29)</t>
+          <t>“BofA Merrill Lynch sent a process letter to Company G requesting a non-binding indication of interest by May 3, 2013” (p. 28)</t>
         </is>
       </c>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>41397</v>
+        <v>41390</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>41397</v>
+        <v>41390</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>41397</v>
+        <v>41390</v>
       </c>
     </row>
     <row r="28">
@@ -2202,18 +2196,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>05/01/2013</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2227,33 +2225,31 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Round 1 due date reached. WDC submitted; G withdrew. Late: Company D, told of the date 04/23, asked on 05/02 for an extra week and submitted 05/10 (#32), which was considered. H entered after the date was set.</t>
+          <t>First contact, bidder-initiated: H (storage industry) approached BofA; no price. BofA sent H an NDA 05/02/2013. H received no process letter.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“On May 1, 2013, Company H contacted representatives of BofA Merrill Lynch expressing an interest in a potential transaction with sTec.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
-        <v>41397</v>
+        <v>41395</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>41397</v>
+        <v>41395</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>41397</v>
+        <v>41395</v>
       </c>
     </row>
     <row r="29">
@@ -2262,12 +2258,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>shortly after 04/24/2013</t>
+          <t>05/02/2013</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2277,7 +2273,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2294,32 +2290,32 @@
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>E said it wanted only limited, select assets, so the special committee ended discussions. Target's decision following E's statement. Undated: “shortly” after F's 04/24 decline; out by 05/16, when only WDC and D advanced (#36).</t>
+          <t>D tells BofA it needs an additional week to confirm its verbal indication in writing, i.e. past the 05/03 due date. No extension by the target is reported.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Company E indicated it was also only interested in purchasing limited, select assets of sTec, and as a result the special committee decided not to continue discussions with Company E.” (p. 28)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="n"/>
+          <t>“Company D’s representatives indicated they would need an additional week to confirm their verbal indication of interest in writing.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>41399</v>
+        <v>41396</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>41388</v>
+        <v>41396</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>41410</v>
+        <v>41396</v>
       </c>
     </row>
     <row r="30">
@@ -2328,12 +2324,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>05/08/2013</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2343,7 +2339,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2352,11 +2348,27 @@
       <c r="G30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="H30" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
@@ -2364,24 +2376,24 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Entry. Late entrant, after the 05/03 due date. NDA includes a “don't ask, don't waive” standstill term surviving signing.</t>
+          <t>Unclear: no conditions reported and diligence still open (data-room access came 05/10). Written indication of interest, $6.60–$7.10 cash, responding to the 04/23 process letter; first priced WDC proposal.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Also on May 8, 2013, sTec entered into a non-disclosure agreement with Company H.” (p. 29)</t>
+          <t>“On May 3, 2013, WDC submitted a written indication of interest to acquire the company at a purchase price in the range of $6.60 – $7.10 per share in cash.” (p. 29)</t>
         </is>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>41402</v>
+        <v>41397</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>41402</v>
+        <v>41397</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>41402</v>
+        <v>41397</v>
       </c>
     </row>
     <row r="31">
@@ -2390,12 +2402,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>05/10/2013</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2405,7 +2417,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2422,28 +2434,32 @@
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access for a late entrant: management presentation to H, after other bidders had theirs in April.</t>
+          <t>G told BofA it would not continue, on the round-1 due date, without submitting an indication; no reason given.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“On May 10, 2013, sTec held a management presentation with Company H.” (p. 29)</t>
+          <t>“Also on May 3, 2013, Company G indicated it would not continue in the process.” (p. 29)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
     </row>
     <row r="32">
@@ -2452,22 +2468,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/10/2013</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2481,31 +2493,33 @@
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Information access: WDC given virtual data room access, four days before Company D (#33). Operating Projections were available to all bidders with data-room access (p. 45).</t>
+          <t>Round-1 due date for WDC, D and G. WDC submitted; G withdrew; D submitted late (05/10) and was allowed to continue (05/15). H, entering later, bid 05/15 without a process letter.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“Also on May 10, 2013, sTec granted access to WDC to the virtual data room.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="n"/>
+          <t>“BofA Merrill Lynch sent process letters to WDC and Company D requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>41404</v>
+        <v>41397</v>
       </c>
     </row>
     <row r="33">
@@ -2514,12 +2528,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/10/2013</t>
+          <t>05/08/2013</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2529,7 +2543,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2538,27 +2552,11 @@
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
@@ -2566,28 +2564,24 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: no data room until 05/14; additional diligence requests pending since 04/23. Written non-binding indication of interest at $5.75 cash; requested exclusivity with a draft exclusivity agreement. Late against the 05/03 due date.</t>
+          <t>Entry. Sixth sale NDA; includes a surviving “don’t ask, don’t waive” standstill. Management presentation to H on 05/10/2013; no data-room access reported for H.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“Company D submitted a written non-binding indication of interest to acquire the company at a purchase price of $5.75 per share in cash, along with a draft exclusivity agreement.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Also on May 8, 2013, sTec entered into a non-disclosure agreement with Company H.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>41404</v>
+        <v>41402</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>41404</v>
+        <v>41402</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>41404</v>
+        <v>41402</v>
       </c>
     </row>
     <row r="34">
@@ -2596,12 +2590,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>05/14/2013</t>
+          <t>05/10/2013</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2632,24 +2626,24 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Information access: D given virtual data room access, four days after WDC (#31).</t>
+          <t>Information access: WDC given virtual data room access (with the Operating Projections, p. 45) before D (05/14); no access reported for H. Diligence calls with WDC and D followed during weeks of 05/13 and 05/20.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“On May 14, 2013, sTec granted access to Company D to the virtual data room.” (p. 29)</t>
+          <t>“Also on May 10, 2013, sTec granted access to WDC to the virtual data room.” (p. 29)</t>
         </is>
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>41408</v>
+        <v>41404</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>41408</v>
+        <v>41404</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>41408</v>
+        <v>41404</v>
       </c>
     </row>
     <row r="35">
@@ -2658,12 +2652,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>05/15/2013</t>
+          <t>05/10/2013</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2683,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>5.75</v>
@@ -2700,7 +2694,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
@@ -2710,24 +2704,28 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: only a management presentation (05/10) reported. Written non-binding indication of interest, range $5.00–$5.75 cash.</t>
+          <t>Heavy: sent with a draft exclusivity agreement, after detailing further diligence needs. Written non-binding indication, $5.75 cash; one week after the 05/03 due date (late, but considered). Confirms and prices the 04/23 verbal indication.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Company H submitted a written non-binding indication of interest to acquire the company at a purchase price in the range of $5.00 – $5.75 per share in cash.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t>“Company D submitted a written non-binding indication of interest to acquire the company at a purchase price of $5.75 per share in cash, along with a draft exclusivity agreement” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
     </row>
     <row r="36">
@@ -2736,7 +2734,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>05/15/2013</t>
+          <t>05/10/2013</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2751,7 +2749,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2772,24 +2770,24 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Target admitted D to continue, with a price requirement: D would need to meaningfully increase its $5.75 proposal (#32) once given more information and access to management. Decided by the chairman for the special committee.</t>
+          <t>Requested: D proposed exclusivity through a draft exclusivity agreement with its bid; period not stated. No exclusivity is reported as executed.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Company D would be allowed to continue in the process with the understanding that Company D would need to meaningfully increase its proposal” (p. 29)</t>
+          <t>“Company D submitted a written non-binding indication of interest to acquire the company at a purchase price of $5.75 per share in cash, along with a draft exclusivity agreement” (p. 29)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>41409</v>
+        <v>41404</v>
       </c>
     </row>
     <row r="37">
@@ -2798,58 +2796,60 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>05/16/2013</t>
+          <t>05/14/2013</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>After the board meeting, final round process letters and a draft merger agreement went to WDC and Company D, with responses due 05/28/2013. Company H not invited (#38). Diligence calls with WDC and D weeks of 05/13 and 05/20.</t>
+          <t>Information access: D given virtual data room access, four days after WDC; H not reported as given access.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch sent final round process letters and a draft merger agreement to WDC and Company D, requesting a response by May 28, 2013.” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“On May 14, 2013, sTec granted access to Company D to the virtual data room.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>41410</v>
+        <v>41408</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>41410</v>
+        <v>41408</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>41410</v>
+        <v>41408</v>
       </c>
     </row>
     <row r="38">
@@ -2858,54 +2858,76 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>weeks of 05/13 and 05/20/2013</t>
+          <t>05/15/2013</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Latham &amp; Watkins</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Target legal adviser (litigation counsel to sTec and to Manouch Moshayedi); first seen acting in diligence calls with WDC and D. Advised the board on 05/30 on the covenant not to sue that WDC requested.</t>
+          <t>Unclear: no conditions reported; H had only a management presentation, no data room. Written non-binding indication, $5.00–$5.75 cash, submitted without a process letter.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Latham &amp; Watkins LLP (“Latham &amp; Watkins”), litigation counsel to sTec and Mr. Manouch Moshayedi, held due diligence calls and meetings with WDC and Company D” (p. 29)</t>
+          <t>“Company H submitted a written non-binding indication of interest to acquire the company at a purchase price in the range of $5.00 – $5.75 per share in cash.” (p. 29)</t>
         </is>
       </c>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>41413</v>
+        <v>41409</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>41407</v>
+        <v>41409</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>41420</v>
+        <v>41409</v>
       </c>
     </row>
     <row r="39">
@@ -2914,19 +2936,15 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>mid-to-late May 2013</t>
+          <t>05/15/2013</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2943,35 +2961,33 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Price requirement and admission: BofA, at the chairman's direction for the special committee, told H its range (#34) was too low to advance but that a revised indication would be considered. Dated after the 05/15 bid and before H's 05/23 reply.</t>
+          <t>Admission with price requirement: at the chairman’s direction for the special committee, BofA tells D it may continue but must meaningfully increase its $5.75 proposal after more information and management access.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“indicated that the price range Company H had submitted was not sufficient to move them forward in the process.” (p. 30)</t>
+          <t>“Company D would be allowed to continue in the process with the understanding that Company D would need to meaningfully increase its proposal” (p. 29)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>41413</v>
+        <v>41409</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>41417</v>
+        <v>41409</v>
       </c>
     </row>
     <row r="40">
@@ -2980,69 +2996,57 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>05/23/2013</t>
+          <t>after the 05/16/2013 board meeting</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>H said it remained interested but could not raise its $5.00–$5.75 range, so it was not advanced under #38. Both sides: the target set the price requirement and H declined to meet it. H later “repeatedly” restated this (p. 34).</t>
+          <t>Round 2: at the board’s direction BofA sent “final round” process letters and a draft merger agreement to WDC and D only, response due 05/28/2013. H not invited (told separately its range was insufficient).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Company H remained interested in a potential acquisition of the company but that Company H was not able to increase its indicated value range.” (p. 30)</t>
+          <t>“BofA Merrill Lynch sent final round process letters and a draft merger agreement to WDC and Company D, requesting a response by May 28, 2013” (p. 30)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>41417</v>
+        <v>41410</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>41417</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>41417</v>
-      </c>
+        <v>41410</v>
+      </c>
+      <c r="V40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3050,12 +3054,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013</t>
+          <t>weeks of 05/13/2013 and 05/20/2013</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Shearman &amp; Sterling</t>
+          <t>Latham &amp; Watkins LLP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
@@ -3080,24 +3084,24 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>WDC's legal counsel; first seen acting by delivering WDC's merger agreement markup on 05/28. Later negotiated the ancillary agreements with Paul Hastings and the merger agreement with Gibson Dunn.</t>
+          <t>Litigation counsel to sTec and to Manouch Moshayedi; first shown acting at due-diligence calls and meetings with WDC and D; later advised on the covenant not to sue WDC requested (05/30).</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“proposed revisions to the merger agreement markup received from Shearman on May 28, 2013” (p. 33)</t>
+          <t>“Latham &amp; Watkins LLP (“Latham &amp; Watkins”), litigation counsel to sTec and Mr. Manouch Moshayedi, held due diligence calls and meetings with WDC and Company D” (p. 29)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>41422</v>
+        <v>41413</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>41422</v>
+        <v>41407</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>41422</v>
+        <v>41420</v>
       </c>
     </row>
     <row r="42">
@@ -3106,22 +3110,18 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013</t>
+          <t>weeks of 05/13/2013 and 05/20/2013 (after the 05/15 bid)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3130,56 +3130,38 @@
       <c r="G42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Contemplated signing by 06/03 (expedited diligence). Required ancillary agreements: officer and director voting agreements, Manouch Moshayedi covenant not to sue, Moshayedi non-competes and technical services, landlord consent. $9.15 cash with a merger agreement markup; WDC called it its highest price.</t>
+          <t>Price requirement: BofA, at the chairman’s direction, tells H its $5.00–$5.75 range is not enough to advance; H may submit a revised indication for the special committee. Window bounded by H’s 05/15 bid and 05/23 reply.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“On May 28, 2013, WDC submitted a written second-round indication of interest at a price per share of $9.15 in cash, with a mark-up of the merger agreement” (p. 30)</t>
+          <t>“indicated that the price range Company H had submitted was not sufficient to move them forward in the process” (p. 30)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>41422</v>
+        <v>41413</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>41422</v>
+        <v>41409</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>41422</v>
+        <v>41417</v>
       </c>
     </row>
     <row r="43">
@@ -3188,12 +3170,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013</t>
+          <t>05/23/2013</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3203,7 +3185,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -3220,32 +3202,36 @@
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="n"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>D did not respond with a bid. It said it remained interested and understood it had to move meaningfully on value, but needed about two more weeks of diligence before submitting a written indication and a markup.</t>
+          <t>H, told its range was insufficient to advance, said it remained interested but could not increase its $5.00–$5.75 range; never admitted to round 2. Special committee later noted H “repeatedly” said it could not raise (p. 34).</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“Company D needed approximately two weeks of additional time to continue its ongoing due diligence review and to submit a written indication of interest and mark-up of the merger agreement.” (p. 30)</t>
+          <t>“Company H remained interested in a potential acquisition of the company but that Company H was not able to increase its indicated value range” (p. 30)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>41422</v>
+        <v>41417</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>41422</v>
+        <v>41417</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>41422</v>
+        <v>41417</v>
       </c>
     </row>
     <row r="44">
@@ -3259,13 +3245,13 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
+          <t>Shearman &amp; Sterling LLP</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3284,19 +3270,15 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Round 2 due date reached. WDC submitted (#41); D did not (#42). Extended by #44.</t>
+          <t>WDC’s legal counsel; earliest dated act is the merger agreement markup received 05/28/2013. Negotiated the merger agreement and ancillary agreements through 06/23/2013.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“requesting a response by May 28, 2013” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“proposed revisions to the merger agreement markup received from Shearman on May 28, 2013” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
         <v>41422</v>
@@ -3314,18 +3296,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>05/29/2013</t>
+          <t>05/28/2013</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3334,38 +3320,52 @@
       <c r="G45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+      <c r="H45" s="4" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Board, after WDC said $9.15 was its highest price and noted internal price concerns, requested “best and final” proposals from WDC and D, due 05/30/2013; BofA delivered the request that day. Moshayedis reminded not to negotiate their own financial terms before price was agreed.</t>
+          <t>Light: contemplated signing by 06/03/2013, so only expedited diligence and documentation left; financing not stated. $9.15 cash with merger-agreement markup and drafts of ancillary agreements (officer/director voting agreements, Moshayedi covenant not to sue, non-competes). WDC called $9.15 its highest price.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“board of directors directed BofA Merrill Lynch to request a “best and final” proposal from WDC and a “best and final” written proposal from Company D by May 30, 2013.” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“WDC submitted a written second-round indication of interest at a price per share of $9.15 in cash, with a mark-up of the merger agreement and drafts of ancillary agreements” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>41423</v>
+        <v>41422</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>41423</v>
+        <v>41422</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>41423</v>
+        <v>41422</v>
       </c>
     </row>
     <row r="46">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/28/2013</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3398,27 +3398,11 @@
       <c r="G46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
@@ -3426,28 +3410,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Ancillary agreements still under review by the Moshayedis' lawyers; diligence to be completed for a 06/03 announcement. Reaffirmed by price confirmation in answer to the best-and-final request: $9.15 carried from #41, WDC's “best possible price”, with price concerns repeated.</t>
+          <t>D did not submit by the round-2 due date: it said it understood it must move meaningfully on value but needed about two more weeks of diligence before submitting a written indication and merger-agreement markup. Not treated as an exit (D stayed engaged).</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“representatives of WDC verbally indicated that WDC’s indication of interest to acquire the company at a price of $9.15 per share was WDC’s best possible price” (p. 31)</t>
+          <t>“Company D needed approximately two weeks of additional time to continue its ongoing due diligence review and to submit a written indication of interest and mark-up of the merger agreement” (p. 30)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q7</t>
+          <t>Q5; Q6</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
     </row>
     <row r="47">
@@ -3456,22 +3440,18 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/28/2013</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3485,39 +3465,33 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>No best-and-final proposal by the 05/30 due date: D again said it needed more time for diligence, though it believed it could be competitive on price given time. Bidder did not submit; the board chose WDC the same day (#48).</t>
+          <t>Round-2 due date. WDC submitted ($9.15 with markup); D did not. Board met 05/29 and took its next step on the bid in hand by requesting best-and-final proposals.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“representatives of Company D reconfirmed they would require additional time to submit a written indication of interest” (p. 31)</t>
+          <t>“BofA Merrill Lynch sent final round process letters and a draft merger agreement to WDC and Company D, requesting a response by May 28, 2013” (p. 30)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>41424</v>
+        <v>41422</v>
       </c>
     </row>
     <row r="48">
@@ -3526,25 +3500,25 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/29/2013</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
+          <t>sTec (BofA Merrill Lynch)</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
@@ -3556,28 +3530,28 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Revised due date reached. WDC reaffirmed $9.15 (#45); D did not submit (#46). The board acted on the bids in hand (#48).</t>
+          <t>Round 3: board directs BofA to request a “best and final” proposal from WDC and a “best and final” written proposal from D, due 05/30/2013; requested later that day. Moshayedis reminded not to negotiate their own financial terms first.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch’s communication on May 29, 2013 seeking the “best and final” proposals from those companies” (p. 31)</t>
+          <t>“directed BofA Merrill Lynch to request a “best and final” proposal from WDC and a “best and final” written proposal from Company D by May 30, 2013” (p. 30)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>41424</v>
+        <v>41423</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>41424</v>
+        <v>41423</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>41424</v>
+        <v>41423</v>
       </c>
     </row>
     <row r="49">
@@ -3601,20 +3575,36 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="n">
         <v>1</v>
       </c>
@@ -3622,17 +3612,17 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: the board unanimously decided to proceed with WDC at $9.15, aiming to announce on 06/03 once diligence and the merger and ancillary agreements were complete. BofA told WDC that day, subject to satisfactory negotiation of those agreements. No exclusivity.</t>
+          <t>Light: WDC still aimed to announce on 06/03/2013; financing not stated. Verbal best-and-final response confirming $9.15 cash (same as #44) as its best possible price and reiterating internal price concerns.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“Our board of directors unanimously determined to move forward with WDC on their proposed terms” (p. 31)</t>
+          <t>“WDC’s indication of interest to acquire the company at a price of $9.15 per share was WDC’s best possible price” (p. 31)</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q3</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S49" s="2" t="n"/>
@@ -3652,12 +3642,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>05/31/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3667,14 +3657,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
@@ -3684,36 +3674,32 @@
       <c r="M50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>WDC said it was reevaluating its interest and “not prepared to move forward … at that time”, and stopped diligence. Bidder's decision, for now. 06/01–06/10: WDC told BofA an internal difference of opinion had emerged and its prior bidding approach had been rejected.</t>
+          <t>D did not submit a best-and-final proposal: it reconfirmed it needed more time for a written indication but believed it could be competitive on price with additional time. Not treated as an exit.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“WDC was reevaluating its interest in acquiring sTec, and that WDC was not prepared to move forward with a transaction with sTec at that time.” (p. 31)</t>
+          <t>“the Company D representatives also indicated they continued to believe they could be competitive on price if given additional time” (p. 31)</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q1; Q8; Q6</t>
         </is>
       </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
     </row>
     <row r="51">
@@ -3722,64 +3708,58 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>05/31/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
-      <c r="M51" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #46. At the board's request BofA told D the timing had been delayed and it could continue; D said it would consider it. On 06/01 sTec posted materials answering D's diligence requests to the data room.</t>
+          <t>Best-and-final due date. WDC confirmed $9.15; D asked for more time. The board moved forward with WDC the same day.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“they informed Company D’s representatives that timing for sTec’s process had been delayed, and that Company D had an opportunity to continue in the process.” (p. 31)</t>
+          <t>“a “best and final” written proposal from Company D by May 30, 2013” (p. 30)</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q1; Q8</t>
         </is>
       </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>41425</v>
+        <v>41424</v>
       </c>
     </row>
     <row r="52">
@@ -3788,68 +3768,58 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>06/05/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>D said it could not actively conduct diligence for more than two weeks and was disengaging. Bidder's decision.</t>
+          <t>Preferred bidder: board unanimously decided to move forward with WDC on its proposed terms, aiming to announce 06/03/2013; BofA told WDC sTec would proceed at $9.15, subject to negotiating the merger and ancillary agreements. No exclusivity reported.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“Company D would not be in a position to actively conduct due diligence for more than two weeks and was disengaging from the process.” (p. 32)</t>
+          <t>“BofA Merrill Lynch informed WDC that sTec would move forward to effect a transaction at a purchase price of $9.15 per share” (p. 31)</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q1; Q8</t>
         </is>
       </c>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>41430</v>
+        <v>41424</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>41430</v>
+        <v>41424</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>41430</v>
+        <v>41424</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3828,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>06/10/2013</t>
+          <t>05/31/2013</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3873,14 +3843,14 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
@@ -3890,32 +3860,36 @@
       <c r="M53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="n"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #49 with a revised written indication (#53), on the 05/28 transaction terms. Between 06/01 and 06/10 BofA held several discussions with WDC, at the board's direction, while WDC reconsidered.</t>
+          <t>WDC said it was re-evaluating and not prepared to proceed “at that time” and stopped due diligence. Over 06/01–06/10 it cited an internal difference of opinion and rejection of its prior bidding approach.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“The representative from WDC also communicated that WDC was otherwise prepared to move forward on the transaction terms previously proposed on May 28, 2013.” (p. 32)</t>
+          <t>“WDC was reevaluating its interest in acquiring sTec, and that WDC was not prepared to move forward with a transaction with sTec at that time” (p. 31)</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>41435</v>
+        <v>41425</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>41435</v>
+        <v>41425</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>41435</v>
+        <v>41425</v>
       </c>
     </row>
     <row r="54">
@@ -3924,80 +3898,58 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/10/2013</t>
+          <t>on or after 05/31/2013</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec (BofA Merrill Lynch)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: WDC stopped diligence 05/31; confirmatory diligence resumed 06/16. Range $6.60–$7.10 cash, down from $9.15 (#41), on the 05/28 markup terms. WDC cited business factors, a changed bidding strategy, and the deal not being essential to it.</t>
+          <t>Target re-invites D: at the board’s request (05/31 meeting) BofA told D the timetable had slipped and D could continue; D said it would consider this. Undated call; bounded by D’s 06/05 disengagement.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“On June 10, 2013, WDC submitted a revised written indication of interest to acquire the company at a price range of $6.60 to $7.10 per share in cash.” (p. 32)</t>
+          <t>“informed Company D’s representatives that timing for sTec’s process had been delayed, and that Company D had an opportunity to continue in the process” (p. 31)</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q1; Q6</t>
         </is>
       </c>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="3" t="n">
-        <v>41435</v>
+        <v>41425</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>41435</v>
+        <v>41425</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>41435</v>
+        <v>41430</v>
       </c>
     </row>
     <row r="55">
@@ -4006,12 +3958,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/11/2013</t>
+          <t>06/01/2013</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4028,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
@@ -4042,12 +3994,12 @@
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: the board would not respond to a range and asked WDC for a specific proposal reflecting its best offer, with confirmation of senior-management support. No due date. The board also conveyed disappointment at the drop from #41.</t>
+          <t>Information access: sTec posted to the data room materials responding to D’s diligence requests, while WDC had suspended diligence.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“informed WDC that our board of directors would not consider a proposal with a range of value and requested that WDC submit a specific proposal reflecting its best offer” (p. 32)</t>
+          <t>“On June 1, 2013, sTec posted materials responsive to the diligence requests of Company D to the data room.” (p. 31)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -4057,13 +4009,13 @@
       </c>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="3" t="n">
-        <v>41436</v>
+        <v>41426</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>41436</v>
+        <v>41426</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>41436</v>
+        <v>41426</v>
       </c>
     </row>
     <row r="56">
@@ -4072,12 +4024,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>06/14/2013</t>
+          <t>06/05/2013</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4087,65 +4039,53 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="2" t="n"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Could announce 06/24 (expedited; confirmatory diligence 06/16–06/22). $6.85 cash, stated as WDC's best and final price, on the 05/28 markup terms. Answers #54.</t>
+          <t>D said it could not actively conduct due diligence for more than two weeks and was disengaging; it never submitted a written indication after 05/10 ($5.75).</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“WDC submitted a written indication of interest of $6.85 per share in cash and indicated it could be in a position to announce a transaction on June 24, 2013” (p. 32)</t>
+          <t>“Company D would not be in a position to actively conduct due diligence for more than two weeks and was disengaging from the process” (p. 32)</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1; Q6</t>
         </is>
       </c>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="3" t="n">
-        <v>41439</v>
+        <v>41430</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>41439</v>
+        <v>41430</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>41439</v>
+        <v>41430</v>
       </c>
     </row>
     <row r="57">
@@ -4154,7 +4094,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>06/15/2013</t>
+          <t>06/10/2013</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4169,14 +4109,14 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
@@ -4190,28 +4130,28 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: the special committee, then the board, decided to proceed with WDC at $6.85 (#55), subject to final agreements, targeting a 06/24 announcement. No counterproposal, for fear WDC would withdraw. WDC told 06/16. No exclusivity.</t>
+          <t>WDC resumes after its 05/31 withdrawal (#52), through BofA discussions over 06/01–06/10 and a revised written indication, stating it was otherwise prepared to proceed on its 05/28 transaction terms.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“the board members present unanimously determined that they believed that it was in the best interests of sTec and its shareholders to move forward with a transaction with WDC” (p. 33)</t>
+          <t>“The representative from WDC also communicated that WDC was otherwise prepared to move forward on the transaction terms previously proposed on May 28, 2013.” (p. 32)</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="3" t="n">
-        <v>41440</v>
+        <v>41435</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>41440</v>
+        <v>41435</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>41440</v>
+        <v>41435</v>
       </c>
     </row>
     <row r="58">
@@ -4220,54 +4160,80 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>06/17/2013</t>
+          <t>06/10/2013</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Paul Hastings</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Counsel to Manouch and Mark Moshayedi; first seen acting when it began negotiating the covenant not to sue and related ancillary agreements with Shearman on 06/17. It won continued indemnification for Manouch Moshayedi, subject to a $20 million cap.</t>
+          <t>Unclear: WDC had stopped diligence 05/31 and did more (06/16–06/22); financing not stated. Revised written indication $6.60–$7.10 cash, down from $9.15, on the 05/28 terms (markup). WDC cited business factors and a changed bidding strategy.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“representatives from Paul Hastings LLP (“Paul Hastings”), counsel to Messrs. Moshayedi, and Shearman &amp; Sterling LLP (“Shearman”), counsel to WDC, commenced negotiating the terms of the covenant not to sue” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="n"/>
+          <t>“On June 10, 2013, WDC submitted a revised written indication of interest to acquire the company at a price range of $6.60 to $7.10 per share in cash.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q7</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="3" t="n">
-        <v>41442</v>
+        <v>41435</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>41442</v>
+        <v>41435</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>41442</v>
+        <v>41435</v>
       </c>
     </row>
     <row r="59">
@@ -4276,25 +4242,25 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>06/19/2013</t>
+          <t>06/11/2013</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Securities</t>
+          <t>sTec (BofA Merrill Lynch)</t>
         </is>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
@@ -4306,24 +4272,28 @@
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>WDC's financial adviser; first seen acting when it received sTec's Cost-Reduction Projections on 06/19. The merger agreement names it as the only broker entitled to a fee.</t>
+          <t>Price requirement: board expressed disappointment, refused to respond to a range, and required a specific best offer confirmed as supported by WDC’s senior management; BofA told WDC the same day.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“Wells Fargo Securities, LLC, WDC’s financial advisor” (p. 46)</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="n"/>
+          <t>“our board of directors would not consider a proposal with a range of value and requested that WDC submit a specific proposal reflecting its best offer” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="3" t="n">
-        <v>41444</v>
+        <v>41436</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>41444</v>
+        <v>41436</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>41444</v>
+        <v>41436</v>
       </c>
     </row>
     <row r="60">
@@ -4332,7 +4302,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>06/19/2013</t>
+          <t>06/14/2013</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4347,20 +4317,36 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="n">
         <v>1</v>
       </c>
@@ -4368,24 +4354,28 @@
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Projections issued after price was agreed: the Cost-Reduction (standalone plan) Projections went to WDC and Wells Fargo; bidders had earlier seen only the Operating Projections (p. 45). A clean team agreement on 06/18 gave WDC representatives further data-room access. Reported in the projections section.</t>
+          <t>Light: remaining diligence described as confirmatory (06/16–06/22); financing not stated (merger agreement later had no financing condition). Written $6.85 cash, called WDC’s best and final, otherwise on its 05/28 terms; announcement possible 06/24/2013. Ref: $3.59 close 06/21/2013; 91% premium.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“Cost-Reduction Projections were also provided to WDC and Wells Fargo Securities, LLC, WDC’s financial advisor, on June 19, 2013, after the parties had agreed upon the per share merger consideration.” (p. 46)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="n"/>
+          <t>“WDC submitted a written indication of interest of $6.85 per share in cash and indicated it could be in a position to announce a transaction on June 24, 2013” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="3" t="n">
-        <v>41444</v>
+        <v>41439</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>41444</v>
+        <v>41439</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>41444</v>
+        <v>41439</v>
       </c>
     </row>
     <row r="61">
@@ -4394,19 +4384,15 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>06/20/2013</t>
+          <t>06/15/2013</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4416,38 +4402,40 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>WDC refused sTec's proposed general waiver of “don't ask, don't waive” standstills (binding E, F, H) and warned it might not proceed if sTec waived unilaterally. The committee judged a superior proposal remote and accepted this on 06/23. WDC also declined further merger agreement negotiation.</t>
+          <t>Preferred bidder: special committee (judging WDC unlikely to raise and a counterproposal risky) and then the board decided to proceed with WDC at $6.85, subject to final terms; BofA told WDC on 06/16/2013.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“Shearman communicated that WDC would not agree to this waiver, and in addition, WDC would view it as improper if sTec unilaterally waived these provisions” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="n"/>
+          <t>“the special committee unanimously determined that they believed that it was in the best interests of sTec and its shareholders to move forward with a transaction with WDC” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="3" t="n">
-        <v>41445</v>
+        <v>41440</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>41445</v>
+        <v>41440</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>41445</v>
+        <v>41440</v>
       </c>
     </row>
     <row r="62">
@@ -4456,48 +4444,42 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>06/23/2013</t>
+          <t>06/17/2013</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Paul Hastings LLP</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="n"/>
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>sTec, WDC and Lodi Ventures (merger sub) signed: $6.85 per share in cash. Voting agreements and Moshayedi ancillary agreements signed. Termination fee $9.4 million; reverse fee $17 million. No financing condition. BofA fairness opinion same day.</t>
+          <t>Counsel to Messrs. Manouch and Mark Moshayedi (founders, 13.8% holders); negotiated with Shearman the covenant not to sue and other agreements the Moshayedis were asked to sign, 06/17–06/23/2013.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“On June 23, 2013, sTec, WDC, and Merger Sub executed the merger agreement” (p. 35)</t>
+          <t>“representatives from Paul Hastings LLP (“Paul Hastings”), counsel to Messrs. Moshayedi” (p. 33)</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -4507,13 +4489,13 @@
       </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="3" t="n">
-        <v>41448</v>
+        <v>41442</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>41448</v>
+        <v>41442</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>41448</v>
+        <v>41442</v>
       </c>
     </row>
     <row r="63">
@@ -4522,60 +4504,384 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013</t>
+          <t>06/18/2013</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G63" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Joint sTec/WDC press release before market open. Ref: $3.59 close 06/21/2013, the last full trading day before announcement (p. 11); 91% premium to the close on the trading day before board approval (p. 36).</t>
+          <t>Information access: clean team agreement gives certain WDC representatives access to further data-room information, during WDC’s confirmatory diligence (06/16–06/22). WDC was then the only live bidder.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“WDC and sTec announced in a joint press release the execution of the merger agreement.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="n"/>
+          <t>“on June 18, 2013, sTec and WDC entered into a “clean team agreement” to allow certain representatives of WDC access to further information in the data room” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="3" t="n">
+        <v>41443</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>41443</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>41443</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>06/19/2013</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Wells Fargo Securities, LLC</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>WDC’s financial adviser; first shown acting when it received sTec’s Cost-Reduction Projections on 06/19/2013 (from the “Certain Financial Projections” section, not the background).</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>“The Cost-Reduction Projections were also provided to WDC and Wells Fargo Securities, LLC, WDC’s financial advisor, on June 19, 2013” (p. 46)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="3" t="n">
+        <v>41444</v>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>41444</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>41444</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>06/19/2013</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Information access (from the projections section, pp. 45–46): standalone Cost-Reduction Projections given to WDC only after price was agreed; bidders earlier got only the Operating Projections, marked as not the standalone plan.</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>“provided to WDC and Wells Fargo Securities, LLC, WDC’s financial advisor, on June 19, 2013, after the parties had agreed upon the per share merger consideration” (p. 46)</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="3" t="n">
+        <v>41444</v>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>41444</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>41444</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>06/20/2013–06/23/2013</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>WDC refuses further merger-agreement negotiation and a waiver of “don’t ask, don’t waive” standstills (E, F, H NDAs), warning it may not proceed if sTec waives unilaterally. Target accepts, judging a superior proposal remote.</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>“Shearman communicated that WDC would not agree to this waiver, and in addition, WDC would view it as improper if sTec unilaterally waived these provisions” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="n"/>
+      <c r="T66" s="3" t="n">
+        <v>41446</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>41445</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>41448</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>06/23/2013</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Signed at $6.85 per share in cash; WDC wins. Special committee and board approved after BofA’s fairness opinion. Voting agreements by officers and directors; Moshayedi ancillary agreements. Termination fees $9.4m (sTec) and $17.0m reverse (WDC); no financing condition.</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>“On June 23, 2013, sTec, WDC, and Merger Sub executed the merger agreement” (p. 8)</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="3" t="n">
+        <v>41448</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>41448</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>41448</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>06/24/2013</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>sTec and WDC</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Joint press release before the market opened announced the signed merger agreement. Balch Hill/Potomac campaign ran until this announcement.</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>“WDC and sTec announced in a joint press release the execution of the merger agreement” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n"/>
+      <c r="S68" s="2" t="n"/>
+      <c r="T68" s="3" t="n">
         <v>41449</v>
       </c>
-      <c r="U63" s="3" t="n">
+      <c r="U68" s="3" t="n">
         <v>41449</v>
       </c>
-      <c r="V63" s="3" t="n">
+      <c r="V68" s="3" t="n">
         <v>41449</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V63"/>
+  <autoFilter ref="A1:V68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4586,19 +4892,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4665,12 +4971,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BofA began contacting potential acquirers at special committee direction (18 discussed in total)</t>
+          <t>BofA Merrill Lynch began contacting potential acquirers (18 in all) at the special committee’s direction; IOI process letters 04/23 (WDC, Company D) and 04/26 (Company G).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>6 strategic, admitted by NDA: Company E, Company D, Company F, Company G, WDC (addendum), Company H (late entrant, NDA 05/08). Contacted but not entered: Companies A and C, the financial sponsor and 9 unnamed technology companies (on the Q2 membership assumption).</t>
+          <t>6 strategic entered during the round: Company E (NDA 04/04), Company D (04/10), Company F (04/11), Company G (04/17), WDC (NDA addendum 04/17), Company H (05/08). IOIs were requested from WDC, Company D and Company G; E and F left before any request. Company H: bid still being received, not admitted (no process letter).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4690,12 +4996,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3: WDC (05/03), Company D (oral 04/23; written 05/10, late), Company H (05/15)</t>
+          <t>3 bidders: WDC ($6.60–$7.10, 05/03); Company D (verbal &gt;$5.60 04/23; $5.75 05/10, late); Company H ($5.00–$5.75, 05/15).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>WDC and D advanced to the final round (05/16). H told it was too low and out 05/23. E dropped; F and G withdrew.</t>
+          <t>Two advanced (WDC, Company D). Out during the round: Company F (withdrew 04/24), Company E (dropped late April), Company G (withdrew 05/03). Company H was told its range was insufficient.</t>
         </is>
       </c>
     </row>
@@ -4711,22 +5017,22 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board sent final round process letters and a draft merger agreement to WDC and Company D</t>
+          <t>“Final round” process letters with a draft merger agreement sent to WDC and Company D after the 05/16 board meeting.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: WDC, Company D. Company H still being received, not admitted (until 05/23).</t>
+          <t>2 strategic: WDC, Company D. Company H still being received, not admitted (invited to submit a revised indication; said 05/23 it could not increase).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013 → 05/30/2013</t>
+          <t>05/28/2013</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Extended; Enforced</t>
+          <t>Enforced</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -4736,17 +5042,63 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1: WDC ($9.15 on 05/28, reaffirmed 05/30; after withdrawing 05/31, $6.60–$7.10 on 06/10 and $6.85 on 06/14). Company D did not submit.</t>
+          <t>1 bidder: WDC ($9.15 cash with merger-agreement markup, 05/28). Company D did not submit and asked for about two weeks.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Signing with WDC at $6.85 (06/23). D withdrew 06/05.</t>
+          <t>Board requested best-and-final proposals from both (round 3). Company H out 05/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>41423</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Board directed BofA to request “best and final” proposals from WDC and Company D by 05/30.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2 strategic: WDC, Company D.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>05/30/2013</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Enforced</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Announced as final</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1 bidder: WDC ($9.15 confirmed 05/30; after withdrawing 05/31 it returned with $6.60–$7.10 on 06/10 and $6.85 best and final on 06/14). Company D never submitted.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Signing with WDC at $6.85 cash (06/23/2013). Company D withdrew 06/05; WDC withdrew 05/31 and re-entered 06/10.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4757,15 +5109,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4814,27 +5166,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: is this one process with two rounds, round 1 opened by BofA's outreach on 04/01/2013 and round 2 by the 05/16/2013 final-round letters, running to signing?</t>
+          <t>Process and round map: one process with three rounds (04/01 outreach; 05/16 “final round” letters; 05/29 best-and-final request)?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. One process. Round 0 holds the pre-outreach approaches (A, B, C, D). Round 1 runs from #12; round 2 from #36. WDC's withdrawal and return and the 06/11 best-offer request stay inside the final round.</t>
+          <t>Keep one process, rounds 1–3, with WDC’s 06/10 and 06/14 bids and the 06/11 request inside round 3.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Only gap of about two months or more: 11/14/2012 (A's contact; the later notice cancelling A's meeting is undated, so the start is uncertain) to 02/13/2013 (B), about three months. C7: (a) met, since nothing was outstanding and nobody was carried forward. (b) not established: no reported end, the board decided to “continue to review” (p. 24), and the gap is at most about three months. (c) met: special committee formed 02/13. The 05/16 letters were “final round” (p. 30).</t>
+          <t>Gap with no reported acquirer contact: 11/14/2012 (Company A; the meeting cancellation is undated) to 02/13/2013 (Company B), at most ~91 days. E5: (a) met: no offer outstanding; (b) not met: the end was not reported and the undated cancellation means a ~3-month gap is not established; (c) met: special committee 02/13/2013. So one process. Round 1 opens at the 04/01 outreach (pp. 24–27). Round 2: 05/16 letters called “final round” but asked for “non-binding proposals” (p. 30). Round 3: the first best-and-final request (p. 30).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#2, #3, #6, #7, #12, #36, #48, #54, #61</t>
+          <t>#1, #2, #3, #4, #5, #11, #12, #13, #39, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61, #62, #63, #64, #65, #66</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Most plausible alternative: round 3 opens at #54 (06/11), when the board asked WDC for a specific best offer after the 05/30 selection collapsed. #54–#61 would move to round 3 (Announced as final; no deadline). A process break at 02/13/2013 is not supported.</t>
+          <t>(i) Open round 1 on the 03/26 decision: #11–12 move into round 1. (ii) Fold the 05/29 request into round 2 as bargaining: #47 is dropped, #48–66 become round 2, and round 2’s due dates become 05/28 → 05/30. (iii) Open round 4 on 06/11 for WDC alone: #58–66 move to round 4. (iv) Two processes split at 02/13/2013: #1–5 become process 1, with a Process restarted row at #6.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4847,27 +5199,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Outreach total: is Company C inside, and Company B outside, the 18 prospective acquirers BofA held discussions with?</t>
+          <t>How do the 18 BofA-contacted prospective acquirers reconcile with the named parties?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. The residual cohort #13 (13 strategic) plus the sponsor #14 and A, C, D and H (individual first-contact rows) adds up to 18.</t>
+          <t>Remainder cohort of technology companies with Count 12–14, the sponsor on its own row, and B and C kept outside the 18.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The filing counts 18 on p. 27 (17 technology, 1 sponsor): 3 whole-company indications (WDC, D, H), 6 asset-only, 9 not interested (including the sponsor and A). C's asset-only statement on 04/15 fits the six. B declined around late February, before BofA was retained (03/26–03/28). But p. 35 cites “17 other potential buyers” contacted “directly or through” management, which could include B. G is necessarily among the 18 but is unclassified.</t>
+          <t>The filing names WDC, H, D, the financial sponsor and Company A as members of the 18 (p. 27). Company B (management contact) and Company C (asset interest) may or may not be among the six asset-only or nine not-interested parties. E, F and G are not placed in any bucket. The 17 other buyers in the reasons section (p. 36) match 18 in total.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#7, #8, #13, #14</t>
+          <t>#7, #8, #9, #14, #15, #19</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If C is outside the 18, Count on #13 becomes 14. If B is inside, it becomes 12 (13 if C is also outside). The type split and the auction screen (six NDA parties) are unchanged.</t>
+          <t>If B and C are among the 18, the remainder is 12; if neither is, 14. Live-bidder counts are unaffected because none of these parties entered.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4880,27 +5232,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: round 1 (05/03/2013) and round 2 (05/28/2013 → 05/30/2013).</t>
+          <t>Round-1 deadline outcome (due 05/03/2013)?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Round 1: Late bids accepted. Round 2: Extended; Enforced.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Round 1: D, told of the 05/03 date on 04/23, asked on 05/02 for another week and bid on 05/10 (#32). The target considered the bid and let D continue (#35); no target revision is reported. H entered after the date was set, so its bid was not late (p. 29). Round 2: the 05/29 best-and-final request moved the date to 05/30 (#44). On 05/30 the board chose WDC on the bids in hand (#48), pp. 30–31.</t>
+          <t>D was given the 05/03 date (p. 28) and said on 05/02 it needed another week. It submitted $5.75 on 05/10, and on 05/15 the target let D continue, conditional on raising its price (p. 29). No extension is reported. WDC met the date and G withdrew on it.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#27, #32, #43, #44, #47, #48</t>
+          <t>#28, #31, #34, #38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If D's extra week counts as a target-granted extension, round 1 becomes Extended. The later invitation to D (#50) followed WDC's withdrawal; if it is read as reopening the 05/30 date, the second round 2 outcome becomes Passed without action.</t>
+          <t>“Extended” if the 05/02 exchange is read as a granted extension. This would not change participation.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4913,27 +5265,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Company H: dropped from the process on 05/23/2013, or still live until signing?</t>
+          <t>How and when did Company H exit?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target on 05/23 (#39), exit reason Would not improve earlier offer.</t>
+          <t>Dropped by target on 05/23/2013, Exit reason “Would not improve earlier offer”.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The target said H's range was “not sufficient to move them forward” but a revised indication would be considered (p. 30). On 05/23 H said it could not increase its range. H was never invited to round 2. The committee later judged a superior proposal from H “remote” (p. 34).</t>
+          <t>BofA told H its range was not sufficient to move forward but that a revised indication would be considered. H replied on 05/23 that it could not increase its range (p. 30). H received no final-round letter and had no later contact except repeated statements that it could not raise (p. 34).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#38, #39</t>
+          <t>#41, #42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If H is treated as still being received until signing (it “repeatedly” restated its range, p. 34), #39 becomes Not selected at signing on 06/23. H would then be one more live unit from 05/23 to 06/23.</t>
+          <t>Not selected at signing (06/23), which would keep H live through rounds 2–3 (3 live units at round 3 instead of 2). Or Withdrew, though H said it “remained interested”.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4946,27 +5298,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Conditions on WDC's $9.15 bid and its reaffirmation: Light or Heavy?</t>
+          <t>Round-2 deadline outcome (due 05/28/2013)?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Light on #41 and #45.</t>
+          <t>Enforced.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The bid contemplated signing by 06/03, so diligence was expedited. On 05/30 the board aimed to “complete diligence” for a 06/03 announcement (p. 31). WDC also required ancillary agreements from the founders, including a covenant not to sue that gave up indemnification rights (pp. 30, 33). These are treated as final documentation. The filing is silent on bid-time financing.</t>
+          <t>On 05/29 the board acted on the bid in hand, WDC’s $9.15 with its markup: it opened a best-and-final request with a 05/30 due date (p. 30). D, which had not submitted, was still invited.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#41, #45</t>
+          <t>#45, #46</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If the founders' covenant not to sue is an unresolved material requirement, both rows become Heavy. That would mark WDC's top bid as more conditional than recorded.</t>
+          <t>If the 05/29 request is folded into round 2 (see the map Question), the outcome becomes “Extended” with due dates 05/28 → 05/30, and round 2 ends with the board’s 05/30 decision.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4979,27 +5331,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Company D after 05/28: exit on 05/30 and re-entry on 05/31, or continuously live until it disengaged on 06/05?</t>
+          <t>Should Company D’s non-submissions on 05/28 and 05/30 be exits (Did not submit), with Re-entered rows?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>As recorded: Did not submit 05/30 (#46), Re-entered 05/31 (#50), Withdrew 06/05 (#51).</t>
+          <t>No: record them as events within the round and a single Withdrew exit on 06/05/2013.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D missed both the 05/28 date and the 05/30 best-and-final date, citing diligence (#42, #46). The board chose WDC on 05/30. After WDC stepped back, BofA told D it “had an opportunity to continue”; D “would consider” it, and on 06/01 sTec posted materials for D (p. 31).</t>
+          <t>Each time, D asked for more time, said it would move meaningfully on value or be competitive, and the target kept inviting it (05/31 call; 06/01 data-room postings). Its participation looks continuous until it disengaged on 06/05 (pp. 30–32).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#42, #46, #50, #51</t>
+          <t>#45, #49, #53, #55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Alternative 1: D was live throughout (#46 and #50 dropped); live units on 05/30–05/31 go from 1 to 2. Alternative 2: D was out on 05/30 and never re-entered, because it only said it would consider; #50 is dropped and #51 is folded into a Note.</t>
+          <t>Add Did not submit rows at 05/28 and 05/30 and Re-entered rows at 05/29 and 05/31. D would then not be live at the round-3 opening, WDC would be the sole round-3 invitee at times, and D’s exit reason on 06/05 would remain.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -5012,27 +5364,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Late reconfirmation (C12): does WDC need a Bid reaffirmed row after the 06/15 decision to proceed at $6.85?</t>
+          <t>WDC’s 05/31 pull-back and 06/10 return: an exit and re-entry? And how should the 05/30 and 06/10 bids be classified?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>No. #45 (05/30) is recorded as Bid reaffirmed by price confirmation, answering the best-and-final request. No row is needed after #56.</t>
+          <t>Withdrew on 05/31 (“at that time”) and Re-entered on 06/10. The 05/30 confirmation is a round-3 Bid (Formal). The 06/10 range is Formal with Conditions Unclear.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>For #56, test (a) holds (decision to finalize with WDC) and test (c) holds (Shearman's revised draft of 06/20, p. 33). Test (b) fails: WDC's latest priced row #55 is Formal in a round announced as final. That bid answered the 06/11 best-offer request and was stated as “best and final” (p. 32).</t>
+          <t>WDC said it was not prepared to proceed and stopped diligence, then returned with a lower written range “otherwise prepared” to proceed on its 05/28 terms, including the markup (pp. 31–32). The 05/30 statement answered a best-and-final request.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#45, #55, #56</t>
+          <t>#48, #52, #56, #57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If #55 were Informal or round 2 Not final, add Bid reaffirmed on 06/20 (by returned draft; $6.85 carried from #55; Conditions Light, with confirmatory diligence 06/16–06/22).</t>
+          <t>Treat WDC as continuously live, with no exit or re-entry. Or mark the 06/10 range Informal, since it was a range the board refused to consider, which lowers the formal-bid count. Or treat 05/30 as no new bid, which leaves round 3 without a pre-withdrawal bid.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -5045,66 +5397,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>WDC's 05/31 statement: a withdrawal followed by re-entry on 06/10, or continuous participation?</t>
+          <t>Round-3 deadline outcome (due 05/30/2013)?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Withdrew on 05/31 (#49), for now, and Re-entered on 06/10 (#52).</t>
+          <t>Enforced.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>WDC said it was “not prepared to move forward … at that time” and stopped diligence (p. 31). It was then “reconsidering its interest” in several talks with BofA between 06/01 and 06/10, and gave serious thought to not proceeding (p. 32).</t>
+          <t>On 05/30, with WDC confirming $9.15 and D asking for more time, the board decided to proceed with WDC and told WDC so (p. 31). After WDC pulled back on 05/31, D was re-invited without a new due date and no further due date was set.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#49, #52</t>
+          <t>#49, #50, #51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>If WDC stayed live, drop #49 and #52. Live units from 05/31 to 06/10 go from 1 to 2 (to 06/05), then from 0 to 1 until 06/10.</t>
+          <t>“Passed without action” if the later re-invitation of D is read as bidding simply continuing. This would not change live-bidder counts.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Is WDC's 06/10 range bid Formal?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Formal, on thin evidence.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>It continues WDC's Formal proposal (#41) in the same process. WDC said it was “prepared to move forward on the transaction terms previously proposed on May 28” (p. 32), which ties the price to its merger agreement markup. Against this: it was a range, unsolicited, after a withdrawal, and the board refused to respond to a range.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>#53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>#53 becomes Informal. #55 stays Formal either way, as the answer to the 06/11 best-offer request.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5118,7 +5437,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -5142,7 +5461,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sTec, Inc. (California)</t>
+          <t>sTec, Inc. (Santa Ana, California; enterprise solid state drives; Nasdaq: STEC)</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Western Digital Corporation (WDC), through its wholly owned subsidiary Lodi Ventures, Inc.</t>
+          <t>Western Digital Corporation (WDC), through Lodi Ventures, Inc., its wholly owned merger subsidiary</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5485,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: WDC is a developer and manufacturer of storage products (p. 7); it has cash on hand and no financing condition (p. 36).</t>
+          <t>Strategic (storage-products manufacturer: WD, HGST and G-Technology brands)</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5497,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$6.85 per share in cash</t>
+          <t>$6.85 per share in cash, without interest; no financing condition. Termination fees: $9.4 million payable by sTec, $17.0 million reverse fee payable by WDC.</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5521,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013 (joint press release before market open)</t>
+          <t>06/24/2013 (joint press release before the market opened)</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5533,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A definitive proxy statement dated 08/07/2013 (supplied file dated 08/08/2013)</t>
+          <t>DEFM14A (definitive proxy statement) dated 08/07/2013; supplied file dated 2013-08-08</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5557,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Target-led. In Q4 2012 the board chose a formal review and market check, before activist Balch Hill's 12/06/2012 letter. Unsolicited approaches (A, B, C, D) came during the review, and BofA's outreach then ran the sale. Activist pressure was concurrent.</t>
+          <t>Target-led. In mid-November 2012 the board decided on a formal review of strategic alternatives including a sale. Activist pressure (Balch Hill 13D 11/16/2012, letter 12/06/2012) came alongside it. Company A, B, C and D approaches preceded the organised outreach.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5581,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Undated, general and exploratory approaches from third parties, with no terms proposed. 2011: WDC's then CEO told sTec's founder at a lunch that WDC wanted to expand in SSDs; no proposal. Summer 2012: a WDC senior vice president asked about the Moshayedis' retirement plans; no further discussion. WDC–sTec mutual NDA dated 01/29/2009 (purpose not stated), brought into this process by a 04/17/2013 addendum.</t>
+          <t>2011: at an industry event, WDC’s then CEO told Manouch Moshayedi that WDC wanted to expand in SSDs. Summer 2012: WDC’s Michael Hajeck asked whether the Moshayedis planned to retire. Neither led to further discussion. Other informal third-party approaches were “general and exploratory”, with no terms proposed (pp. 23–24).</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5593,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 6 parties: Companies E, D, F, G and H (new NDAs) and WDC (addendum to its 2009 NDA). The filing's total of “six non-disclosure agreements” counts agreements; here that equals parties. No post-signing additions (no go-shop).</t>
+          <t>Met (process 1): 6 parties (WDC by NDA addendum; Companies D, E, F, G, H)</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5629,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch (sole; approved 03/26/2013, engagement letter 03/28/2013)</t>
+          <t>BofA Merrill Lynch</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5641,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Gibson, Dunn &amp; Crutcher (outside corporate counsel, engaged October 2012); Latham &amp; Watkins (litigation counsel to sTec and Manouch Moshayedi). Proxy solicitor: MacKenzie Partners.</t>
+          <t>Gibson, Dunn &amp; Crutcher LLP (corporate counsel); Latham &amp; Watkins LLP (litigation counsel to sTec and Manouch Moshayedi)</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5653,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Facing losses and activist pressure, sTec's board began a strategic review in late 2012 and formed a special committee in February 2013. After unsolicited contacts from Companies A–D, BofA contacted 18 prospective acquirers from 04/01/2013, and six signed NDAs. WDC ($6.60–$7.10), D ($5.75) and H ($5.00–$5.75) made non-binding indications; the others wanted only assets or dropped out. In the final round WDC bid $9.15 with a merger agreement markup and confirmed it as best and final, while D asked for more time; the board chose WDC on 05/30. WDC withdrew the next day and returned on 06/10 at $6.60–$7.10, while D disengaged. Pressed for a single best offer, WDC bid $6.85, which was signed on 06/23/2013 and announced 06/24/2013.</t>
+          <t>Facing losses and activist pressure, sTec’s board began a review including a sale in late 2012, formed a special committee in February 2013 and hired BofA Merrill Lynch in March. From 04/01/2013, BofA contacted 18 prospective acquirers, six signed NDAs, and WDC, Company D and Company H made indications from $5.00 to $7.10. WDC and D advanced to a final round, where WDC bid $9.15 with a merger-agreement markup while D kept asking for more time. After the board chose WDC at $9.15, WDC pulled back on 05/31, D disengaged on 06/05, and WDC returned at $6.60–$7.10 and then $6.85 best and final. The board accepted, and the merger agreement was signed on 06/23/2013 and announced on 06/24/2013.</t>
         </is>
       </c>
     </row>

--- a/extraction/stec.xlsx
+++ b/extraction/stec.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,10 +68,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,28 +439,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -604,8 +604,8 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -614,7 +614,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Target’s outside corporate (legal) counsel, engaged October 2012; advised the board and special committee on fiduciary duties and negotiated the merger agreement with WDC’s counsel.</t>
+          <t>Target's legal adviser: engaged October 2012 as outside corporate counsel; advised the board and special committee on fiduciary duties and negotiated the merger agreement with WDC's counsel.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -622,19 +622,15 @@
           <t>“which had been engaged in October 2012 as the company’s outside corporate counsel” (p. 25)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="4" t="n">
         <v>41198</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>41183</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>41213</v>
       </c>
     </row>
@@ -668,8 +664,8 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -680,27 +676,23 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>First contact, bidder-initiated via Company A’s (unnamed) investment bank; no price. Bank sent agenda and draft NDA for “a possible business transaction”. Scheduled meeting later cancelled (undated) over non-management directors’ concerns; no NDA signed. Company A later told BofA it was not interested (p. 27).</t>
+          <t>First contact, bidder-initiated: Company A's (unnamed) investment bank asked for a preliminary meeting, then sent an agenda and a draft NDA. No price; no NDA executed. Company A was later among the nine not interested in the April 2013 outreach.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“On November 14, 2012, an investment bank representing Company A, a participant in the storage industry, contacted our management to request a preliminary meeting between sTec and Company A.” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“an investment bank representing Company A, a participant in the storage industry, contacted our management to request a preliminary meeting between sTec and Company A” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="4" t="n">
         <v>41227</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>41227</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="4" t="n">
         <v>41227</v>
       </c>
     </row>
@@ -710,7 +702,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>mid-November 2012</t>
+          <t>after 11/14/2012</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -721,7 +713,7 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -730,8 +722,8 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
@@ -740,29 +732,23 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Board, weighing cost cuts, decided to undertake a formal review of strategic alternatives including a potential sale (a market check versus standalone), and authorized management to contact financial advisers. Two advisers contacted declined; none engaged; board continued the review.</t>
+          <t>Target cancelled the scheduled meeting with Company A because non-management directors were concerned Company A's management had not shown involvement; concern communicated to Company A. Cancellation date not stated.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“in mid-November, 2012, our board of directors authorized management to contact potential financial advisors to explore their interest in representing the company in its exploration of strategic alternatives” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“it was subsequently cancelled because of concerns expressed by non-management board members, which were communicated to Company A” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="3" t="n">
-        <v>41228</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>41224</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>41232</v>
-      </c>
+      <c r="T4" s="4" t="n">
+        <v>41227</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>41227</v>
+      </c>
+      <c r="V4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -770,18 +756,18 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>11/16/2012</t>
+          <t>mid-November 2012</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Balch Hill Partners, L.P.</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Activist</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -790,8 +776,8 @@
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
@@ -800,28 +786,24 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Activist Balch Hill filed its first Schedule 13D, reporting 6.4%; later joined by Potomac Capital Partners II (together 9.8%). Campaign continued until the merger announcement and included nominating three directors for the 2013 annual meeting.</t>
+          <t>Board, having decided on a formal review of alternatives including a possible sale (a market check against a standalone cost-reduction plan), authorized management to approach financial advisers; the two contacted both declined and no adviser was engaged then.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“Balch Hill filed its first Schedule 13D with the SEC on November 16, 2012.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“in mid-November, 2012, our board of directors authorized management to contact potential financial advisors to explore their interest in representing the company” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
-      <c r="T5" s="3" t="n">
-        <v>41229</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>41229</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>41229</v>
+      <c r="T5" s="4" t="n">
+        <v>41228</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>41224</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>41232</v>
       </c>
     </row>
     <row r="6">
@@ -830,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>11/16/2012</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -850,8 +832,8 @@
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -860,28 +842,24 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Balch Hill amended its 13D and wrote to the board urging cost cuts, a focus on SAS-interface products and exploration of strategic alternatives; it and Potomac advocated reversing sTec’s new go-to-market strategy.</t>
+          <t>Activist investor (technology sector) filed its first Schedule 13D, reporting 6.4% of sTec shares. Later joined by Potomac Capital Partners II, L.P.; jointly 9.8%.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“on December 6, 2012, Balch Hill filed an amendment to its Schedule 13D, and concurrently issued a letter to our board of directors urging our board to reduce costs” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Balch Hill filed its first Schedule 13D with the SEC on November 16, 2012.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
-      <c r="T6" s="3" t="n">
-        <v>41249</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>41249</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>41249</v>
+      <c r="T6" s="4" t="n">
+        <v>41229</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>41229</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>41229</v>
       </c>
     </row>
     <row r="7">
@@ -890,18 +868,18 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>02/13/2013</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
+          <t>Balch Hill Partners, L.P.</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Activist</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -910,8 +888,8 @@
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -920,24 +898,24 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Board formed a special committee of independent directors (Daly, Colpitts, Witte; Bahri added 03/26/2013) to review strategic alternatives including a sale versus standalone cost cuts, authorized to engage a financial adviser. Nine banks then canvassed; three interviewed late February.</t>
+          <t>With a 13D amendment, Balch Hill wrote to the board urging cost cuts, a SAS focus and exploration of strategic alternatives. With Potomac it kept up the campaign, including nominating three directors for the 2013 annual meeting, until the merger announcement.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“The mandate of the special committee was to conduct a review of sTec’s strategic alternatives, including a possible sale of the company” (p. 25)</t>
+          <t>“concurrently issued a letter to our board of directors urging our board to reduce costs, focus on products with a SAS interface, and explore strategic alternatives” (p. 25)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
-      <c r="T7" s="3" t="n">
-        <v>41318</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>41318</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>41318</v>
+      <c r="T7" s="4" t="n">
+        <v>41249</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>41249</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>41249</v>
       </c>
     </row>
     <row r="8">
@@ -951,17 +929,13 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Company B</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -970,39 +944,33 @@
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>First contact: Company B’s President (electronics industry) told Manouch Moshayedi he would present sTec to B’s management as a possible acquisition target; no price. sTec then forwarded B a presentation on its technology and business (undated). No NDA reported.</t>
+          <t>Board formed a special committee of independent directors (Daly, Colpitts, Witte; Bahri added 03/26) to review alternatives including a possible sale or standalone cost cuts, authorized to hire a financial adviser. From 02/14, nine banks were sounded out and three interviewed in late February.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“the President intended to present sTec as a possible acquisition target to the management of Company B” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“The mandate of the special committee was to conduct a review of sTec’s strategic alternatives, including a possible sale of the company” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="4" t="n">
         <v>41318</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="4" t="n">
         <v>41318</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="4" t="n">
         <v>41318</v>
       </c>
     </row>
@@ -1012,7 +980,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>about two weeks after sTec sent Company B a presentation (after 02/13/2013)</t>
+          <t>02/13/2013</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1027,7 +995,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1036,8 +1004,8 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -1048,27 +1016,25 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Company B declines: its executive management was not interested in acquiring sTec and could develop the needed technology internally. Company B never entered (no NDA or bid), so no exit label. Sort date set about two weeks after the earliest possible forwarding date.</t>
+          <t>First contact: Company B's President (electronics industry) told Manouch Moshayedi he would present sTec to Company B management as a possible acquisition target; sTec sent a business presentation. About two weeks later Company B declined, believing it could develop the technology itself. Never entered.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Company B’s management had determined that it was not interested in acquiring sTec and believed that it could independently develop the technology it needed to compete in enterprise SSDs” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“the President intended to present sTec as a possible acquisition target to the management of Company B” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
-      <c r="T9" s="3" t="n">
-        <v>41332</v>
-      </c>
-      <c r="U9" s="3" t="n">
+      <c r="T9" s="4" t="n">
         <v>41318</v>
       </c>
-      <c r="V9" s="2" t="n"/>
+      <c r="U9" s="4" t="n">
+        <v>41318</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>41318</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1091,7 +1057,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1100,8 +1066,8 @@
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1112,27 +1078,27 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Bidder-initiated contact during an ordinary business meeting: Company C (semiconductor industry) expressed potential interest in acquiring particular assets of sTec and said it was considering submitting an acquisition proposal. No price; no NDA reported.</t>
+          <t>First contact, during an ordinary business meeting: Company C (semiconductor industry) expressed potential interest in acquiring particular assets of sTec's business, not the whole company, and said it was considering an acquisition proposal. No price.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“the representatives of Company C, among other matters, expressed a potential interest in exploring an acquisition of particular assets of sTec’s business” (p. 26)</t>
+          <t>“expressed a potential interest in exploring an acquisition of particular assets of sTec’s business” (p. 26)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="3" t="n">
+      <c r="T10" s="4" t="n">
         <v>41346</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="4" t="n">
         <v>41346</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="4" t="n">
         <v>41346</v>
       </c>
     </row>
@@ -1166,33 +1132,35 @@
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>First contact, bidder-initiated: Company D’s head of corporate development contacted management about acquiring sTec; no price. Management met D at the special committee’s direction; D sent a draft NDA on 03/26/2013.</t>
+          <t>First contact, bidder-initiated: Company D's head of corporate development expressed interest in acquiring sTec; management met Company D at the special committee's direction. Company D sent a draft NDA on 03/26 (executed 04/10). No price.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“Company D, a participant in the storage industry, contacted our management to express the interest of Company D in exploring a potential acquisition of the company” (p. 27)</t>
+          <t>“the head of corporate development for Company D, a participant in the storage industry, contacted our management to express the interest of Company D in exploring a potential acquisition” (p. 27)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
-      <c r="T11" s="3" t="n">
+      <c r="T11" s="4" t="n">
         <v>41348</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="4" t="n">
         <v>41344</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="4" t="n">
         <v>41352</v>
       </c>
     </row>
@@ -1222,8 +1190,8 @@
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
@@ -1232,7 +1200,7 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target’s financial adviser. Board approved retention on the special committee’s recommendation for the strategic review and defensive preparedness; engagement letter signed 03/28/2013. Delivered the 06/23/2013 fairness opinion.</t>
+          <t>Target's financial adviser: board approved retaining it on the special committee's recommendation, subject to terms; engagement letter signed 03/28/2013. Fee about $4.3 million, mostly contingent on completion; it has had banking relationships with WDC (p. 44).</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1240,19 +1208,15 @@
           <t>“the board approved retaining BofA Merrill Lynch to act as sTec’s financial advisor in connection with the company’s general review of strategic alternatives and defensive preparedness” (p. 27)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="4" t="n">
         <v>41359</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="4" t="n">
         <v>41359</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="4" t="n">
         <v>41359</v>
       </c>
     </row>
@@ -1282,8 +1246,8 @@
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
@@ -1292,7 +1256,7 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Board decided to confidentially approach the strategic buyers most likely to be interested and to conduct a limited confirmatory exploration of financial buyers (noting their lack of interest and debt-financing difficulty); directed BofA accordingly.</t>
+          <t>Board decided to approach confidentially the strategic buyers most likely to be interested, with only a limited confirmatory check of financial buyers (seen as uninterested given sTec's results and debt-financing difficulty), and had BofA told of this approach.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1300,19 +1264,15 @@
           <t>“to confidentially approach strategic buyers that the board believed would be most likely to have interest in a potential acquisition of the company to explore their interest” (p. 27)</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="4" t="n">
         <v>41359</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="4" t="n">
         <v>41359</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="4" t="n">
         <v>41359</v>
       </c>
     </row>
@@ -1327,7 +1287,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -1342,8 +1302,8 @@
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1352,7 +1312,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opens with BofA’s outreach wave to a list agreed with management; no due date at opening. Virtual data room populated from early April; management presentations to WDC, D, G and E during weeks of 04/08–04/22.</t>
+          <t>BofA, as directed by the special committee, began contacting potential acquirers from a list set with management. A data room was populated from early April; management presentations to WDC, Company D, Company G and Company E in the weeks of 04/08–04/22. No due date at opening.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1362,17 +1322,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="4" t="n">
         <v>41365</v>
       </c>
     </row>
@@ -1387,12 +1347,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial sponsor</t>
+          <t>Technology companies contacted in BofA outreach (residual, incl. WDC)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1406,39 +1366,39 @@
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated contact by BofA; the only financial sponsor among the 18 prospective acquirers BofA spoke with. It indicated it was not interested; never entered.</t>
+          <t>Count: 12–14. Target-initiated. Filing total: BofA held discussions with 18 prospective acquirers (17 technology, 1 financial sponsor): 3 whole-company IOIs (WDC, H, D), 6 strategic asset-only, 9 not interested (incl. sponsor, A). Residual = 17 technology − H, D, A (own rows) − B and C if members (uncertain).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“nine prospective acquirers, including the financial sponsor and Company A, indicated they were not interested in a potential transaction” (p. 27)</t>
+          <t>“In total, BofA Merrill Lynch had discussions with 18 prospective acquirers, 17 of which were technology companies and one of which was a financial sponsor.” (p. 27)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S15" s="2" t="n"/>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="V15" s="2" t="n"/>
+      <c r="V15" s="4" t="n">
+        <v>41448</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1451,12 +1411,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Technology companies contacted by BofA (remainder of 17)</t>
+          <t>Unnamed financial sponsor</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1470,37 +1430,37 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Count: 12–14. Target-initiated BofA contacts. Filing total 18 (17 technology companies, 1 sponsor); A, D, H and the sponsor have own rows; B and C may be among the 17. Includes WDC. Outcomes of all 18: 3 whole-company IOIs (WDC, H, D), 6 asset-only interests, 9 not interested.</t>
+          <t>Target-initiated contact with the only financial sponsor approached, in line with the board's 'limited confirmatory exploration' of financial buyers; it said it was not interested. No NDA; never entered.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“In total, BofA Merrill Lynch had discussions with 18 prospective acquirers, 17 of which were technology companies and one of which was a financial sponsor.” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“nine prospective acquirers, including the financial sponsor and Company A, indicated they were not interested in a potential transaction” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
-      <c r="T16" s="3" t="n">
+      <c r="T16" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" s="4" t="n">
         <v>41365</v>
       </c>
-      <c r="V16" s="2" t="n"/>
+      <c r="V16" s="4" t="n">
+        <v>41448</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1532,8 +1492,8 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
@@ -1544,7 +1504,7 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA includes a “don’t ask, don’t waive” standstill that survives signing. One of six NDAs executed for the sale. Management presentation held during weeks of 04/08–04/22.</t>
+          <t>Entry. NDA contained a 'don't ask, don't waive' standstill term that survived signing. Company E attended a management presentation in the weeks of 04/08–04/22.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1554,13 +1514,13 @@
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
-      <c r="T17" s="3" t="n">
+      <c r="T17" s="4" t="n">
         <v>41368</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="4" t="n">
         <v>41368</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="4" t="n">
         <v>41368</v>
       </c>
     </row>
@@ -1594,8 +1554,8 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
@@ -1606,7 +1566,7 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA (no surviving “don’t ask, don’t waive” term). Management presentation held during weeks of 04/08–04/22; follow-up diligence weeks of 04/22 and 04/29.</t>
+          <t>Entry (draft received from Company D on 03/26). No surviving 'don't ask, don't waive' term. Management presentation in the weeks of 04/08–04/22; follow-up diligence weeks of 04/22–04/29.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1616,13 +1576,13 @@
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="4" t="n">
         <v>41374</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="4" t="n">
         <v>41374</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="4" t="n">
         <v>41374</v>
       </c>
     </row>
@@ -1656,8 +1616,8 @@
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
@@ -1668,23 +1628,23 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA includes a “don’t ask, don’t waive” standstill that survives signing.</t>
+          <t>Entry. Company F is a storage-industry participant; its NDA contained a 'don't ask, don't waive' standstill term that survived signing.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“on April 11, it entered into a non-disclosure agreement with Company F” (p. 27)</t>
+          <t>“on April 11, it entered into a non-disclosure agreement with Company F, another” (p. 27)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="4" t="n">
         <v>41375</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="4" t="n">
         <v>41375</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="4" t="n">
         <v>41375</v>
       </c>
     </row>
@@ -1699,10 +1659,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>Company C</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -1714,37 +1678,39 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Target ends discussions with Company C after C said it wanted only limited, select assets (scope, not a whole-company bid). C never entered, so no exit row.</t>
+          <t>Target ended discussions: Company C said it wanted only limited, select assets, and the special committee decided not to continue. Company C never signed an NDA or bid, so it has no exit row.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“it was only interested in purchasing limited, select assets of the company, and as a result, the special committee decided not to continue discussions with Company C” (p. 28)</t>
+          <t>“Company C indicated that it was only interested in purchasing limited, select assets of the company, and as a result, the special committee decided not to continue discussions” (p. 28)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="4" t="n">
         <v>41379</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" s="4" t="n">
         <v>41379</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="4" t="n">
         <v>41379</v>
       </c>
     </row>
@@ -1778,8 +1744,8 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -1790,7 +1756,7 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Entry. NDA (no surviving “don’t ask, don’t waive” term). Management presentation during weeks of 04/08–04/22; follow-up diligence weeks of 04/22 and 04/29.</t>
+          <t>Entry. Management presentation in the weeks of 04/08–04/22; follow-up diligence materials and BofA discussions weeks of 04/22–04/29.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1800,13 +1766,13 @@
       </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="4" t="n">
         <v>41381</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="4" t="n">
         <v>41381</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="4" t="n">
         <v>41381</v>
       </c>
     </row>
@@ -1840,8 +1806,8 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -1852,7 +1818,7 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Entry. Addendum to an existing WDC NDA (original date not stated), counted among six sale NDAs. WDC contacted in BofA outreach (in the 18). Management presentation 04/18/2013; follow-up diligence weeks of 04/22 and 04/29.</t>
+          <t>Entry: special addendum to WDC's existing mutual NDA of 01/29/2009 (with Western Digital Technologies; Annex A definition, p. A-3); the filing counts it among six sale NDAs. Management presentation to WDC 04/18.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -1862,13 +1828,13 @@
       </c>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="4" t="n">
         <v>41381</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="4" t="n">
         <v>41381</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="4" t="n">
         <v>41381</v>
       </c>
     </row>
@@ -1883,7 +1849,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -1898,8 +1864,8 @@
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -1908,7 +1874,7 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Process letters to WDC and Company D request non-binding indications of interest by 05/03/2013. Company G got the same request 04/26/2013; E, F and H received none.</t>
+          <t>BofA, at the special committee's direction, sent process letters to WDC and Company D asking for non-binding indications of interest by 05/03/2013.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -1916,15 +1882,19 @@
           <t>“BofA Merrill Lynch sent process letters to WDC and Company D requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
         </is>
       </c>
-      <c r="R23" s="2" t="n"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
-      <c r="T23" s="3" t="n">
+      <c r="T23" s="4" t="n">
         <v>41387</v>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="U23" s="4" t="n">
         <v>41387</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="4" t="n">
         <v>41387</v>
       </c>
     </row>
@@ -1958,10 +1928,10 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="3" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1984,7 +1954,7 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Heavy: D detailed additional diligence requirements before any written indication. Verbal; price “greater than $5.60” (lower bound only). Consideration form not stated. Board later discussed confidentiality concerns about D’s diligence requests (04/25).</t>
+          <t>Heavy: Company D set out additional diligence requirements before it would give a written indication. Oral indication on a call with management and BofA at a price 'greater than $5.60 per share' (Price low = that floor). Directors discussed confidentiality concerns about its requests on 04/25.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -1994,13 +1964,13 @@
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
-      <c r="T24" s="3" t="n">
+      <c r="T24" s="4" t="n">
         <v>41387</v>
       </c>
-      <c r="U24" s="3" t="n">
+      <c r="U24" s="4" t="n">
         <v>41387</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="4" t="n">
         <v>41387</v>
       </c>
     </row>
@@ -2034,8 +2004,8 @@
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -2050,7 +2020,7 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>F declined a management presentation, saying it wanted only limited, select assets; no further communication with BofA or sTec.</t>
+          <t>Company F declined to schedule a management presentation, saying it wanted only limited, select assets; no further communication with BofA or sTec.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2058,15 +2028,19 @@
           <t>“on April 24, Company F declined the invitation to schedule a management presentation, indicating it was only interested in purchasing limited, select assets of sTec” (p. 28)</t>
         </is>
       </c>
-      <c r="R25" s="2" t="n"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
-      <c r="T25" s="3" t="n">
+      <c r="T25" s="4" t="n">
         <v>41388</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="U25" s="4" t="n">
         <v>41388</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="4" t="n">
         <v>41388</v>
       </c>
     </row>
@@ -2100,8 +2074,8 @@
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -2116,7 +2090,7 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>E said it wanted only limited, select assets; the special committee decided not to continue discussions. E was not among parties given follow-up diligence (weeks of 04/22 and 04/29) or process letters.</t>
+          <t>Company E said it wanted only limited, select assets; as a result the special committee decided not to continue discussions (the target's decision). Its 'don't ask, don't waive' term remained in force at signing.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2124,15 +2098,19 @@
           <t>“Company E indicated it was also only interested in purchasing limited, select assets of sTec, and as a result the special committee decided not to continue discussions with Company E” (p. 28)</t>
         </is>
       </c>
-      <c r="R26" s="2" t="n"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
+      <c r="T26" s="4" t="n">
         <v>41388</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="4" t="n">
         <v>41388</v>
       </c>
-      <c r="V26" s="2" t="n"/>
+      <c r="V26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2145,7 +2123,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -2160,8 +2138,8 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
@@ -2170,7 +2148,7 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Process letter to Company G, sent at the chairman’s direction for the special committee, requests a non-binding indication of interest by the same 05/03/2013 date.</t>
+          <t>BofA, at the chairman's direction for the special committee, sent Company G a process letter asking for a non-binding indication of interest by 05/03/2013, the due date already given to WDC and Company D.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -2178,15 +2156,19 @@
           <t>“BofA Merrill Lynch sent a process letter to Company G requesting a non-binding indication of interest by May 3, 2013” (p. 28)</t>
         </is>
       </c>
-      <c r="R27" s="2" t="n"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
-      <c r="T27" s="3" t="n">
+      <c r="T27" s="4" t="n">
         <v>41390</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="4" t="n">
         <v>41390</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="4" t="n">
         <v>41390</v>
       </c>
     </row>
@@ -2220,8 +2202,8 @@
       <c r="G28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
@@ -2232,7 +2214,7 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>First contact, bidder-initiated: H (storage industry) approached BofA; no price. BofA sent H an NDA 05/02/2013. H received no process letter.</t>
+          <t>First contact, bidder-initiated, after outreach began: Company H (storage industry) approached BofA; BofA sent an NDA on 05/02 at the chairman's direction. No price. Company H never received a process letter.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2242,13 +2224,13 @@
       </c>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
-      <c r="T28" s="3" t="n">
+      <c r="T28" s="4" t="n">
         <v>41395</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" s="4" t="n">
         <v>41395</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="4" t="n">
         <v>41395</v>
       </c>
     </row>
@@ -2258,12 +2240,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/02/2013</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2273,7 +2255,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2282,11 +2264,27 @@
       <c r="G29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
@@ -2294,28 +2292,24 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>D tells BofA it needs an additional week to confirm its verbal indication in writing, i.e. past the 05/03 due date. No extension by the target is reported.</t>
+          <t>Unclear: no conditions reported and diligence still open (data room access came 05/10). Written indication of interest, on time for the 05/03 due date; the letters asked for non-binding indications.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Company D’s representatives indicated they would need an additional week to confirm their verbal indication of interest in writing.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“WDC submitted a written indication of interest to acquire the company at a purchase price in the range of $6.60 – $7.10 per share in cash” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>41396</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>41396</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>41396</v>
+      <c r="T29" s="4" t="n">
+        <v>41397</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>41397</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>41397</v>
       </c>
     </row>
     <row r="30">
@@ -2329,7 +2323,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2339,7 +2333,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2348,51 +2342,39 @@
       <c r="G30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="n"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no conditions reported and diligence still open (data-room access came 05/10). Written indication of interest, $6.60–$7.10 cash, responding to the 04/23 process letter; first priced WDC proposal.</t>
+          <t>On the indication due date Company G said it would not continue in the process; no reason given.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“On May 3, 2013, WDC submitted a written indication of interest to acquire the company at a purchase price in the range of $6.60 – $7.10 per share in cash.” (p. 29)</t>
+          <t>“Also on May 3, 2013, Company G indicated it would not continue in the process.” (p. 29)</t>
         </is>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="3" t="n">
+      <c r="T30" s="4" t="n">
         <v>41397</v>
       </c>
-      <c r="U30" s="3" t="n">
+      <c r="U30" s="4" t="n">
         <v>41397</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="4" t="n">
         <v>41397</v>
       </c>
     </row>
@@ -2407,17 +2389,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2426,39 +2404,37 @@
       <c r="G31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>G told BofA it would not continue, on the round-1 due date, without submitting an indication; no reason given.</t>
+          <t>Indication due date for WDC, Company D and Company G. WDC bid; Company G withdrew; Company D said on 05/02 it needed another week, bid on 05/10 and was kept in the process. Company H (no letter) bid 05/15.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Also on May 3, 2013, Company G indicated it would not continue in the process.” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>“requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
-      <c r="T31" s="3" t="n">
+      <c r="T31" s="4" t="n">
         <v>41397</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="4" t="n">
         <v>41397</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="4" t="n">
         <v>41397</v>
       </c>
     </row>
@@ -2468,18 +2444,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>05/08/2013</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2488,38 +2468,36 @@
       <c r="G32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Round-1 due date for WDC, D and G. WDC submitted; G withdrew; D submitted late (05/10) and was allowed to continue (05/15). H, entering later, bid 05/15 without a process letter.</t>
+          <t>Entry; the sixth and last sale NDA. It contained a 'don't ask, don't waive' standstill term that survived signing.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch sent process letters to WDC and Company D requesting non-binding indications of interest by May 3, 2013” (p. 28)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Also on May 8, 2013, sTec entered into a non-disclosure agreement with Company H.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
-      <c r="T32" s="3" t="n">
-        <v>41397</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>41397</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>41397</v>
+      <c r="T32" s="4" t="n">
+        <v>41402</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>41402</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>41402</v>
       </c>
     </row>
     <row r="33">
@@ -2528,7 +2506,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/08/2013</t>
+          <t>05/10/2013</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2543,7 +2521,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2552,8 +2530,8 @@
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
@@ -2564,24 +2542,24 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Entry. Sixth sale NDA; includes a surviving “don’t ask, don’t waive” standstill. Management presentation to H on 05/10/2013; no data-room access reported for H.</t>
+          <t>Catch-up access for a late entrant: management presentation to Company H (WDC, D, G and E had theirs in the weeks of 04/08–04/22). No data room access is reported for Company H.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“Also on May 8, 2013, sTec entered into a non-disclosure agreement with Company H.” (p. 29)</t>
+          <t>“On May 10, 2013, sTec held a management presentation with Company H.” (p. 29)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>41402</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>41402</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>41402</v>
+      <c r="T33" s="4" t="n">
+        <v>41404</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>41404</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>41404</v>
       </c>
     </row>
     <row r="34">
@@ -2614,8 +2592,8 @@
       <c r="G34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
@@ -2626,7 +2604,7 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Information access: WDC given virtual data room access (with the Operating Projections, p. 45) before D (05/14); no access reported for H. Diligence calls with WDC and D followed during weeks of 05/13 and 05/20.</t>
+          <t>Information access: WDC given virtual data room access after its indication, four days before Company D; none reported for Company H. Data room bidders received the Operating Projections, marked as not the standalone plan (p. 45).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2636,13 +2614,13 @@
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="4" t="n">
         <v>41404</v>
       </c>
     </row>
@@ -2676,10 +2654,10 @@
       <c r="G35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="3" t="n">
         <v>5.75</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="3" t="n">
         <v>5.75</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2694,7 +2672,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
@@ -2704,7 +2682,7 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Heavy: sent with a draft exclusivity agreement, after detailing further diligence needs. Written non-binding indication, $5.75 cash; one week after the 05/03 due date (late, but considered). Confirms and prices the 04/23 verbal indication.</t>
+          <t>Unclear: no conditions reported; diligence still open (data room access 05/14; more diligence sought later). Written non-binding indication confirming its 04/23 oral one, a week after the 05/03 due date; the target considered it (#38).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2714,17 +2692,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
-      <c r="T35" s="3" t="n">
+      <c r="T35" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="U35" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="4" t="n">
         <v>41404</v>
       </c>
     </row>
@@ -2758,8 +2736,8 @@
       <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
@@ -2770,23 +2748,23 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Requested: D proposed exclusivity through a draft exclusivity agreement with its bid; period not stated. No exclusivity is reported as executed.</t>
+          <t>Requested: Company D sent a draft exclusivity agreement with its indication; length not stated. No exclusivity was executed with any bidder.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Company D submitted a written non-binding indication of interest to acquire the company at a purchase price of $5.75 per share in cash, along with a draft exclusivity agreement” (p. 29)</t>
+          <t>“along with a draft exclusivity agreement” (p. 29)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" s="4" t="n">
         <v>41404</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="4" t="n">
         <v>41404</v>
       </c>
     </row>
@@ -2820,8 +2798,8 @@
       <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
@@ -2832,7 +2810,7 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Information access: D given virtual data room access, four days after WDC; H not reported as given access.</t>
+          <t>Information access: Company D given virtual data room access, four days after WDC; none reported for Company H. Diligence calls and meetings followed with WDC and Company D only, weeks of 05/13 and 05/20.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -2842,13 +2820,13 @@
       </c>
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
-      <c r="T37" s="3" t="n">
+      <c r="T37" s="4" t="n">
         <v>41408</v>
       </c>
-      <c r="U37" s="3" t="n">
+      <c r="U37" s="4" t="n">
         <v>41408</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="4" t="n">
         <v>41408</v>
       </c>
     </row>
@@ -2882,10 +2860,10 @@
       <c r="G38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="3" t="n">
         <v>5.75</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2910,23 +2888,23 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Unclear: no conditions reported; H had only a management presentation, no data room. Written non-binding indication, $5.00–$5.75 cash, submitted without a process letter.</t>
+          <t>Unclear: no conditions reported; Company H had had only a management presentation, with no data room access reported. Written non-binding indication; Company H had no process letter.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Company H submitted a written non-binding indication of interest to acquire the company at a purchase price in the range of $5.00 – $5.75 per share in cash.” (p. 29)</t>
+          <t>“Company H submitted a written non-binding indication of interest to acquire the company at a purchase price in the range of $5.00 – $5.75 per share in cash” (p. 29)</t>
         </is>
       </c>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
-      <c r="T38" s="3" t="n">
+      <c r="T38" s="4" t="n">
         <v>41409</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="4" t="n">
         <v>41409</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="4" t="n">
         <v>41409</v>
       </c>
     </row>
@@ -2941,10 +2919,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2956,17 +2938,19 @@
       <c r="G39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Admission with price requirement: at the chairman’s direction for the special committee, BofA tells D it may continue but must meaningfully increase its $5.75 proposal after more information and management access.</t>
+          <t>Admission with a price requirement: BofA told Company D, at the chairman's direction for the committee, that it could continue if it would meaningfully increase its $5.75 proposal after more information and access to management.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -2974,19 +2958,15 @@
           <t>“Company D would be allowed to continue in the process with the understanding that Company D would need to meaningfully increase its proposal” (p. 29)</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+      <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
-      <c r="T39" s="3" t="n">
+      <c r="T39" s="4" t="n">
         <v>41409</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" s="4" t="n">
         <v>41409</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="4" t="n">
         <v>41409</v>
       </c>
     </row>
@@ -2996,12 +2976,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>after the 05/16/2013 board meeting</t>
+          <t>after 05/16/2013</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D40" s="2" t="n"/>
@@ -3016,8 +2996,8 @@
       <c r="G40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
@@ -3026,7 +3006,7 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Round 2: at the board’s direction BofA sent “final round” process letters and a draft merger agreement to WDC and D only, response due 05/28/2013. H not invited (told separately its range was insufficient).</t>
+          <t>After the 05/16 board meeting, BofA sent final-round process letters and a draft merger agreement to WDC and Company D only, with responses due 05/28/2013 (this sets the due date). Company H not invited.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -3036,17 +3016,19 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="4" t="n">
         <v>41410</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" s="4" t="n">
         <v>41410</v>
       </c>
-      <c r="V40" s="2" t="n"/>
+      <c r="V40" s="4" t="n">
+        <v>41422</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3054,7 +3036,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>weeks of 05/13/2013 and 05/20/2013</t>
+          <t>weeks of 05/13 and 05/20/2013</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3074,8 +3056,8 @@
       <c r="G41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
@@ -3084,23 +3066,23 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Litigation counsel to sTec and to Manouch Moshayedi; first shown acting at due-diligence calls and meetings with WDC and D; later advised on the covenant not to sue WDC requested (05/30).</t>
+          <t>Litigation counsel to sTec and to Manouch Moshayedi (a target legal adviser); joined diligence calls and meetings with WDC and Company D, and on 05/30 advised the board on WDC's requested covenant not to sue.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Latham &amp; Watkins LLP (“Latham &amp; Watkins”), litigation counsel to sTec and Mr. Manouch Moshayedi, held due diligence calls and meetings with WDC and Company D” (p. 29)</t>
+          <t>“representatives of Latham &amp; Watkins LLP (“Latham &amp; Watkins”), litigation counsel to sTec and Mr. Manouch Moshayedi, held due diligence calls and meetings with WDC and Company D” (p. 29)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
-      <c r="T41" s="3" t="n">
+      <c r="T41" s="4" t="n">
         <v>41413</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="U41" s="4" t="n">
         <v>41407</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="4" t="n">
         <v>41420</v>
       </c>
     </row>
@@ -3110,15 +3092,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>weeks of 05/13/2013 and 05/20/2013 (after the 05/15 bid)</t>
+          <t>weeks of 05/13 and 05/20/2013, after 05/15</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -3128,40 +3114,42 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: BofA, at the chairman’s direction, tells H its $5.00–$5.75 range is not enough to advance; H may submit a revised indication for the special committee. Window bounded by H’s 05/15 bid and 05/23 reply.</t>
+          <t>Refused next stage: BofA, at the chairman's direction, told Company H its $5.00–$5.75 range was not enough to move forward, but that a revised indication would be considered by the special committee.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“indicated that the price range Company H had submitted was not sufficient to move them forward in the process” (p. 30)</t>
+          <t>“the price range Company H had submitted was not sufficient to move them forward in the process” (p. 30)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
-      <c r="T42" s="3" t="n">
-        <v>41413</v>
-      </c>
-      <c r="U42" s="3" t="n">
+      <c r="T42" s="4" t="n">
+        <v>41414</v>
+      </c>
+      <c r="U42" s="4" t="n">
         <v>41409</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>41417</v>
+      <c r="V42" s="4" t="n">
+        <v>41420</v>
       </c>
     </row>
     <row r="43">
@@ -3192,10 +3180,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -3210,7 +3198,7 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>H, told its range was insufficient to advance, said it remained interested but could not increase its $5.00–$5.75 range; never admitted to round 2. Special committee later noted H “repeatedly” said it could not raise (p. 34).</t>
+          <t>Company H said it remained interested but could not raise its $5.00–$5.75 range. Having been told that range was insufficient (#41), it was not admitted to the final round.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -3220,17 +3208,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S43" s="2" t="n"/>
-      <c r="T43" s="3" t="n">
+      <c r="T43" s="4" t="n">
         <v>41417</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="U43" s="4" t="n">
         <v>41417</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="4" t="n">
         <v>41417</v>
       </c>
     </row>
@@ -3260,8 +3248,8 @@
       <c r="G44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -3270,7 +3258,7 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>WDC’s legal counsel; earliest dated act is the merger agreement markup received 05/28/2013. Negotiated the merger agreement and ancillary agreements through 06/23/2013.</t>
+          <t>WDC's legal counsel; first shown acting with the merger agreement markup received 05/28; negotiated the Moshayedi agreements from 06/17 and the merger agreement through 06/23.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -3280,13 +3268,13 @@
       </c>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
-      <c r="T44" s="3" t="n">
+      <c r="T44" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="U44" s="3" t="n">
+      <c r="U44" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="4" t="n">
         <v>41422</v>
       </c>
     </row>
@@ -3320,10 +3308,10 @@
       <c r="G45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="3" t="n">
         <v>9.15</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" s="3" t="n">
         <v>9.15</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3348,23 +3336,27 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Light: contemplated signing by 06/03/2013, so only expedited diligence and documentation left; financing not stated. $9.15 cash with merger-agreement markup and drafts of ancillary agreements (officer/director voting agreements, Moshayedi covenant not to sue, non-competes). WDC called $9.15 its highest price.</t>
+          <t>Light: it contemplated signing by 06/03, leaving only expedited diligence; no financing condition reported. Formal: merger agreement markup and draft ancillary agreements, answering the final-round letter. WDC called $9.15 its highest price and noted internal concerns about the price (p. 30).</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“WDC submitted a written second-round indication of interest at a price per share of $9.15 in cash, with a mark-up of the merger agreement and drafts of ancillary agreements” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="n"/>
+          <t>“WDC submitted a written second-round indication of interest at a price per share of $9.15 in cash, with a mark-up of the merger agreement” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="n"/>
-      <c r="T45" s="3" t="n">
+      <c r="T45" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="U45" s="3" t="n">
+      <c r="U45" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="4" t="n">
         <v>41422</v>
       </c>
     </row>
@@ -3379,17 +3371,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3398,19 +3386,17 @@
       <c r="G46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>D did not submit by the round-2 due date: it said it understood it must move meaningfully on value but needed about two more weeks of diligence before submitting a written indication and merger-agreement markup. Not treated as an exit (D stayed engaged).</t>
+          <t>Final-round due date. WDC bid $9.15 with a markup. Company D did not submit; it said it was still interested, knew it had to move meaningfully on value, and needed about two more weeks.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3420,17 +3406,17 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Q5; Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
-      <c r="T46" s="3" t="n">
+      <c r="T46" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="U46" s="3" t="n">
+      <c r="U46" s="4" t="n">
         <v>41422</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="4" t="n">
         <v>41422</v>
       </c>
     </row>
@@ -3440,7 +3426,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013</t>
+          <t>05/29/2013</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3451,7 +3437,7 @@
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3460,8 +3446,8 @@
       <c r="G47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
@@ -3470,28 +3456,28 @@
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Round-2 due date. WDC submitted ($9.15 with markup); D did not. Board met 05/29 and took its next step on the bid in hand by requesting best-and-final proposals.</t>
+          <t>Board directed BofA to ask WDC for a 'best and final' proposal and Company D for a 'best and final' written proposal, both by 05/30; BofA made the requests later that day.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch sent final round process letters and a draft merger agreement to WDC and Company D, requesting a response by May 28, 2013” (p. 30)</t>
+          <t>“directed BofA Merrill Lynch to request a “best and final” proposal from WDC and a “best and final” written proposal from Company D by May 30, 2013” (p. 30)</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S47" s="2" t="n"/>
-      <c r="T47" s="3" t="n">
-        <v>41422</v>
-      </c>
-      <c r="U47" s="3" t="n">
-        <v>41422</v>
-      </c>
-      <c r="V47" s="3" t="n">
-        <v>41422</v>
+      <c r="T47" s="4" t="n">
+        <v>41423</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>41423</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>41423</v>
       </c>
     </row>
     <row r="48">
@@ -3500,28 +3486,28 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>05/29/2013</t>
+          <t>05/30/2013</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
+          <t>sTec</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
@@ -3530,28 +3516,28 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Round 3: board directs BofA to request a “best and final” proposal from WDC and a “best and final” written proposal from D, due 05/30/2013; requested later that day. Moshayedis reminded not to negotiate their own financial terms first.</t>
+          <t>Best-and-final due date. WDC orally confirmed $9.15 as its best possible price, restated its concern about price and aimed to announce 06/03 (no new Bid row). Company D again asked for more time, saying it could be competitive on price.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“directed BofA Merrill Lynch to request a “best and final” proposal from WDC and a “best and final” written proposal from Company D by May 30, 2013” (p. 30)</t>
+          <t>“representatives of WDC verbally indicated that WDC’s indication of interest to acquire the company at a price of $9.15 per share was WDC’s best possible price” (p. 31)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
-      <c r="T48" s="3" t="n">
-        <v>41423</v>
-      </c>
-      <c r="U48" s="3" t="n">
-        <v>41423</v>
-      </c>
-      <c r="V48" s="3" t="n">
-        <v>41423</v>
+      <c r="T48" s="4" t="n">
+        <v>41424</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>41424</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>41424</v>
       </c>
     </row>
     <row r="49">
@@ -3565,74 +3551,48 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Light: WDC still aimed to announce on 06/03/2013; financing not stated. Verbal best-and-final response confirming $9.15 cash (same as #44) as its best possible price and reiterating internal price concerns.</t>
+          <t>Preferred bidder: board unanimously decided to proceed with WDC on its proposed terms, aiming to finish diligence and documents for a 06/03 announcement; BofA told WDC sTec would proceed at $9.15, subject to agreement negotiations. No exclusivity.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“WDC’s indication of interest to acquire the company at a price of $9.15 per share was WDC’s best possible price” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
+          <t>“Our board of directors unanimously determined to move forward with WDC on their proposed terms” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
-      <c r="T49" s="3" t="n">
+      <c r="T49" s="4" t="n">
         <v>41424</v>
       </c>
-      <c r="U49" s="3" t="n">
+      <c r="U49" s="4" t="n">
         <v>41424</v>
       </c>
-      <c r="V49" s="3" t="n">
+      <c r="V49" s="4" t="n">
         <v>41424</v>
       </c>
     </row>
@@ -3642,12 +3602,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/31/2013</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3657,49 +3617,53 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="2" t="n"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>D did not submit a best-and-final proposal: it reconfirmed it needed more time for a written indication but believed it could be competitive on price with additional time. Not treated as an exit.</t>
+          <t>WDC said it was re-evaluating its interest and not prepared to move forward 'at that time' (for now), and stopped due diligence. In talks from 06/01 to 06/10 it cited an internal difference of opinion and rejection of its prior bidding approach.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“the Company D representatives also indicated they continued to believe they could be competitive on price if given additional time” (p. 31)</t>
+          <t>“WDC was reevaluating its interest in acquiring sTec, and that WDC was not prepared to move forward with a transaction with sTec at that time” (p. 31)</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q8; Q6</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S50" s="2" t="n"/>
-      <c r="T50" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="U50" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="V50" s="3" t="n">
-        <v>41424</v>
+      <c r="T50" s="4" t="n">
+        <v>41425</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>41425</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>41425</v>
       </c>
     </row>
     <row r="51">
@@ -3708,7 +3672,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>05/31/2013</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3719,7 +3683,7 @@
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3728,38 +3692,42 @@
       <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Best-and-final due date. WDC confirmed $9.15; D asked for more time. The board moved forward with WDC the same day.</t>
+          <t>Inferred: after WDC's withdrawal undid the round-2 selection, the board had BofA tell Company D the timing had slipped and it could continue; on 06/01 sTec posted Company D's requested diligence materials. BofA also talked with WDC 06/01–06/10 at board direction. No due date.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“a “best and final” written proposal from Company D by May 30, 2013” (p. 30)</t>
+          <t>“informed Company D’s representatives that timing for sTec’s process had been delayed, and that Company D had an opportunity to continue in the process” (p. 31)</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q8</t>
+          <t>Q2; Q8</t>
         </is>
       </c>
       <c r="S51" s="2" t="n"/>
-      <c r="T51" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>41424</v>
+      <c r="T51" s="4" t="n">
+        <v>41425</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>41425</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>41425</v>
       </c>
     </row>
     <row r="52">
@@ -3768,18 +3736,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>06/05/2013</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3788,38 +3760,44 @@
       <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Other stated reason</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: board unanimously decided to move forward with WDC on its proposed terms, aiming to announce 06/03/2013; BofA told WDC sTec would proceed at $9.15, subject to negotiating the merger and ancillary agreements. No exclusivity reported.</t>
+          <t>Company D said it could not actively conduct due diligence for more than two weeks and was disengaging. It had not submitted by the 05/28 or 05/30 due dates; that is recorded as continued participation, not a separate Did not submit exit.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“BofA Merrill Lynch informed WDC that sTec would move forward to effect a transaction at a purchase price of $9.15 per share” (p. 31)</t>
+          <t>“Company D would not be in a position to actively conduct due diligence for more than two weeks and was disengaging from the process” (p. 32)</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S52" s="2" t="n"/>
-      <c r="T52" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="U52" s="3" t="n">
-        <v>41424</v>
-      </c>
-      <c r="V52" s="3" t="n">
-        <v>41424</v>
+      <c r="T52" s="4" t="n">
+        <v>41430</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>41430</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>41430</v>
       </c>
     </row>
     <row r="53">
@@ -3828,7 +3806,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>05/31/2013</t>
+          <t>06/10/2013</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3843,7 +3821,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -3852,44 +3830,40 @@
       <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>WDC said it was re-evaluating and not prepared to proceed “at that time” and stopped due diligence. Over 06/01–06/10 it cited an internal difference of opinion and rejection of its prior bidding approach.</t>
+          <t>WDC returned with a revised written indication (#53) after the 06/01–06/10 talks with BofA, during which it said it was reconsidering its interest.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“WDC was reevaluating its interest in acquiring sTec, and that WDC was not prepared to move forward with a transaction with sTec at that time” (p. 31)</t>
+          <t>“were reconsidering their interest in a transaction with sTec” (p. 32)</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S53" s="2" t="n"/>
-      <c r="T53" s="3" t="n">
-        <v>41425</v>
-      </c>
-      <c r="U53" s="3" t="n">
-        <v>41425</v>
-      </c>
-      <c r="V53" s="3" t="n">
-        <v>41425</v>
+      <c r="T53" s="4" t="n">
+        <v>41435</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>41435</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>41435</v>
       </c>
     </row>
     <row r="54">
@@ -3898,18 +3872,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>on or after 05/31/2013</t>
+          <t>06/10/2013</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -3918,38 +3896,56 @@
       <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
+      <c r="H54" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Target re-invites D: at the board’s request (05/31 meeting) BofA told D the timetable had slipped and D could continue; D said it would consider this. Undated call; bounded by D’s 06/05 disengagement.</t>
+          <t>Unclear: WDC had stopped diligence on 05/31 and no condition is stated. Formal: WDC was 'otherwise prepared to move forward' on its 05/28 terms, which included its merger agreement markup. It lowered the price from $9.15, citing business factors and a change in bidding strategy.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“informed Company D’s representatives that timing for sTec’s process had been delayed, and that Company D had an opportunity to continue in the process” (p. 31)</t>
+          <t>“WDC submitted a revised written indication of interest to acquire the company at a price range of $6.60 to $7.10 per share in cash” (p. 32)</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q6</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="S54" s="2" t="n"/>
-      <c r="T54" s="3" t="n">
-        <v>41425</v>
-      </c>
-      <c r="U54" s="3" t="n">
-        <v>41425</v>
-      </c>
-      <c r="V54" s="3" t="n">
-        <v>41430</v>
+      <c r="T54" s="4" t="n">
+        <v>41435</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>41435</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>41435</v>
       </c>
     </row>
     <row r="55">
@@ -3958,19 +3954,15 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/01/2013</t>
+          <t>06/11/2013</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -3982,40 +3974,34 @@
       <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Information access: sTec posted to the data room materials responding to D’s diligence requests, while WDC had suspended diligence.</t>
+          <t>Price requirement: board had BofA tell WDC that day it was disappointed, would not consider a range, and wanted one specific best offer confirmed as backed by WDC senior management. No due date set.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“On June 1, 2013, sTec posted materials responsive to the diligence requests of Company D to the data room.” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“our board of directors would not consider a proposal with a range of value and requested that WDC submit a specific proposal reflecting its best offer” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
-      <c r="T55" s="3" t="n">
-        <v>41426</v>
-      </c>
-      <c r="U55" s="3" t="n">
-        <v>41426</v>
-      </c>
-      <c r="V55" s="3" t="n">
-        <v>41426</v>
+      <c r="T55" s="4" t="n">
+        <v>41436</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>41436</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>41436</v>
       </c>
     </row>
     <row r="56">
@@ -4024,12 +4010,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2013</t>
+          <t>06/14/2013</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Company D</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4039,7 +4025,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -4048,44 +4034,56 @@
       <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>D said it could not actively conduct due diligence for more than two weeks and was disengaging; it never submitted a written indication after 05/10 ($5.75).</t>
+          <t>Light: WDC could announce by 06/24, leaving only expedited diligence (confirmatory calls 06/16–06/22); no financing condition reported. Formal: answers the best-offer request on its 05/28 terms, including its markup. WDC called $6.85 its best and final price.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“Company D would not be in a position to actively conduct due diligence for more than two weeks and was disengaging from the process” (p. 32)</t>
+          <t>“WDC submitted a written indication of interest of $6.85 per share in cash and indicated it could be in a position to announce a transaction on June 24, 2013” (p. 32)</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q6</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S56" s="2" t="n"/>
-      <c r="T56" s="3" t="n">
-        <v>41430</v>
-      </c>
-      <c r="U56" s="3" t="n">
-        <v>41430</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>41430</v>
+      <c r="T56" s="4" t="n">
+        <v>41439</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>41439</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>41439</v>
       </c>
     </row>
     <row r="57">
@@ -4094,22 +4092,18 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>06/10/2013</t>
+          <t>06/15/2013</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -4118,40 +4112,34 @@
       <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>WDC resumes after its 05/31 withdrawal (#52), through BofA discussions over 06/01–06/10 and a revised written indication, stating it was otherwise prepared to proceed on its 05/28 transaction terms.</t>
+          <t>Preferred bidder: special committee judged WDC unlikely to go higher and a counterproposal risky; committee and board decided to proceed at $6.85, subject to final terms, aiming for a 06/24 announcement. BofA told WDC on 06/16.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“The representative from WDC also communicated that WDC was otherwise prepared to move forward on the transaction terms previously proposed on May 28, 2013.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
+          <t>“it was unlikely that WDC would raise its price further and there was a significant risk that WDC would withdraw the indication of interest if sTec responded with a counterproposal” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
-      <c r="T57" s="3" t="n">
-        <v>41435</v>
-      </c>
-      <c r="U57" s="3" t="n">
-        <v>41435</v>
-      </c>
-      <c r="V57" s="3" t="n">
-        <v>41435</v>
+      <c r="T57" s="4" t="n">
+        <v>41440</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>41440</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>41440</v>
       </c>
     </row>
     <row r="58">
@@ -4160,22 +4148,18 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>06/10/2013</t>
+          <t>06/17/2013</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Paul Hastings LLP</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -4184,56 +4168,34 @@
       <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Unclear: WDC had stopped diligence 05/31 and did more (06/16–06/22); financing not stated. Revised written indication $6.60–$7.10 cash, down from $9.15, on the 05/28 terms (markup). WDC cited business factors and a changed bidding strategy.</t>
+          <t>Counsel to Manouch and Mark Moshayedi (founders; 13.8% combined): negotiated their covenant not to sue and other ancillary agreements with WDC's counsel from 06/17 to 06/23.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“On June 10, 2013, WDC submitted a revised written indication of interest to acquire the company at a price range of $6.60 to $7.10 per share in cash.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
+          <t>“representatives from Paul Hastings LLP (“Paul Hastings”), counsel to Messrs. Moshayedi, and Shearman &amp; Sterling LLP (“Shearman”), counsel to WDC, commenced negotiating” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
-      <c r="T58" s="3" t="n">
-        <v>41435</v>
-      </c>
-      <c r="U58" s="3" t="n">
-        <v>41435</v>
-      </c>
-      <c r="V58" s="3" t="n">
-        <v>41435</v>
+      <c r="T58" s="4" t="n">
+        <v>41442</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>41442</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>41442</v>
       </c>
     </row>
     <row r="59">
@@ -4242,15 +4204,19 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>06/11/2013</t>
+          <t>06/18/2013</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>sTec (BofA Merrill Lynch)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4262,38 +4228,36 @@
       <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: board expressed disappointment, refused to respond to a range, and required a specific best offer confirmed as supported by WDC’s senior management; BofA told WDC the same day.</t>
+          <t>Information access: sTec and WDC signed a clean team agreement giving some WDC representatives further data room information during confirmatory diligence (06/16–06/22). WDC was then the only live bidder.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“our board of directors would not consider a proposal with a range of value and requested that WDC submit a specific proposal reflecting its best offer” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“on June 18, 2013, sTec and WDC entered into a “clean team agreement” to allow certain representatives of WDC access to further information in the data room” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
-      <c r="T59" s="3" t="n">
-        <v>41436</v>
-      </c>
-      <c r="U59" s="3" t="n">
-        <v>41436</v>
-      </c>
-      <c r="V59" s="3" t="n">
-        <v>41436</v>
+      <c r="T59" s="4" t="n">
+        <v>41443</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>41443</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>41443</v>
       </c>
     </row>
     <row r="60">
@@ -4302,22 +4266,18 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>06/14/2013</t>
+          <t>06/20/2013–06/23/2013</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>sTec</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
@@ -4326,56 +4286,34 @@
       <c r="G60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Light: remaining diligence described as confirmatory (06/16–06/22); financing not stated (merger agreement later had no financing condition). Written $6.85 cash, called WDC’s best and final, otherwise on its 05/28 terms; announcement possible 06/24/2013. Ref: $3.59 close 06/21/2013; 91% premium.</t>
+          <t>Post-signing competition limited: WDC refused a general waiver of the surviving 'don't ask, don't waive' standstills (Companies E, F, H) and warned it might not proceed if sTec waived them; on 06/23 committee and board judged a superior proposal remote and went ahead. On 06/20 WDC also refused further merger agreement negotiation.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“WDC submitted a written indication of interest of $6.85 per share in cash and indicated it could be in a position to announce a transaction on June 24, 2013” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Shearman communicated that WDC would not agree to this waiver” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
-      <c r="T60" s="3" t="n">
-        <v>41439</v>
-      </c>
-      <c r="U60" s="3" t="n">
-        <v>41439</v>
-      </c>
-      <c r="V60" s="3" t="n">
-        <v>41439</v>
+      <c r="T60" s="4" t="n">
+        <v>41446</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>41445</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>41448</v>
       </c>
     </row>
     <row r="61">
@@ -4384,18 +4322,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>06/15/2013</t>
+          <t>06/23/2013</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>sTec</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n"/>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -4404,38 +4346,36 @@
       <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: special committee (judging WDC unlikely to raise and a counterproposal risky) and then the board decided to proceed with WDC at $6.85, subject to final terms; BofA told WDC on 06/16/2013.</t>
+          <t>sTec, WDC and Lodi Ventures (merger sub) signed: $6.85 per share in cash, no financing condition, no-shop with a fiduciary out, $9.4 million termination fee. Officers and directors signed voting agreements; the Moshayedis signed ancillary agreements. BofA gave its fairness opinion that day.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“the special committee unanimously determined that they believed that it was in the best interests of sTec and its shareholders to move forward with a transaction with WDC” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“On June 23, 2013, sTec, WDC, and Merger Sub executed the merger agreement” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
-      <c r="T61" s="3" t="n">
-        <v>41440</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>41440</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>41440</v>
+      <c r="T61" s="4" t="n">
+        <v>41448</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>41448</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>41448</v>
       </c>
     </row>
     <row r="62">
@@ -4444,28 +4384,30 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>06/17/2013</t>
+          <t>06/24/2013</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Paul Hastings LLP</t>
+          <t>sTec and WDC</t>
         </is>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
@@ -4474,414 +4416,28 @@
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Counsel to Messrs. Manouch and Mark Moshayedi (founders, 13.8% holders); negotiated with Shearman the covenant not to sue and other agreements the Moshayedis were asked to sign, 06/17–06/23/2013.</t>
+          <t>Joint press release before the market opened. Ref: $3.59 close 06/21/2013, the last full trading day before announcement (p. 11); the board cites a 91% premium to the close on the trading day before approval (p. 36).</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“representatives from Paul Hastings LLP (“Paul Hastings”), counsel to Messrs. Moshayedi” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“WDC and sTec announced in a joint press release the execution of the merger agreement” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
-      <c r="T62" s="3" t="n">
-        <v>41442</v>
-      </c>
-      <c r="U62" s="3" t="n">
-        <v>41442</v>
-      </c>
-      <c r="V62" s="3" t="n">
-        <v>41442</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>06/18/2013</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Other material event</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>Information access: clean team agreement gives certain WDC representatives access to further data-room information, during WDC’s confirmatory diligence (06/16–06/22). WDC was then the only live bidder.</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>“on June 18, 2013, sTec and WDC entered into a “clean team agreement” to allow certain representatives of WDC access to further information in the data room” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="n"/>
-      <c r="T63" s="3" t="n">
-        <v>41443</v>
-      </c>
-      <c r="U63" s="3" t="n">
-        <v>41443</v>
-      </c>
-      <c r="V63" s="3" t="n">
-        <v>41443</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>06/19/2013</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Wells Fargo Securities, LLC</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Adviser</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="n"/>
-      <c r="L64" s="2" t="n"/>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>WDC’s financial adviser; first shown acting when it received sTec’s Cost-Reduction Projections on 06/19/2013 (from the “Certain Financial Projections” section, not the background).</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>“The Cost-Reduction Projections were also provided to WDC and Wells Fargo Securities, LLC, WDC’s financial advisor, on June 19, 2013” (p. 46)</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="n"/>
-      <c r="T64" s="3" t="n">
-        <v>41444</v>
-      </c>
-      <c r="U64" s="3" t="n">
-        <v>41444</v>
-      </c>
-      <c r="V64" s="3" t="n">
-        <v>41444</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>06/19/2013</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Other material event</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
-      <c r="M65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>Information access (from the projections section, pp. 45–46): standalone Cost-Reduction Projections given to WDC only after price was agreed; bidders earlier got only the Operating Projections, marked as not the standalone plan.</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>“provided to WDC and Wells Fargo Securities, LLC, WDC’s financial advisor, on June 19, 2013, after the parties had agreed upon the per share merger consideration” (p. 46)</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="n"/>
-      <c r="T65" s="3" t="n">
-        <v>41444</v>
-      </c>
-      <c r="U65" s="3" t="n">
-        <v>41444</v>
-      </c>
-      <c r="V65" s="3" t="n">
-        <v>41444</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>06/20/2013–06/23/2013</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Other material event</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>WDC refuses further merger-agreement negotiation and a waiver of “don’t ask, don’t waive” standstills (E, F, H NDAs), warning it may not proceed if sTec waives unilaterally. Target accepts, judging a superior proposal remote.</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>“Shearman communicated that WDC would not agree to this waiver, and in addition, WDC would view it as improper if sTec unilaterally waived these provisions” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="n"/>
-      <c r="T66" s="3" t="n">
-        <v>41446</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>41445</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>41448</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>06/23/2013</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Merger agreement signed</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Signed at $6.85 per share in cash; WDC wins. Special committee and board approved after BofA’s fairness opinion. Voting agreements by officers and directors; Moshayedi ancillary agreements. Termination fees $9.4m (sTec) and $17.0m reverse (WDC); no financing condition.</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>“On June 23, 2013, sTec, WDC, and Merger Sub executed the merger agreement” (p. 8)</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="n"/>
-      <c r="T67" s="3" t="n">
-        <v>41448</v>
-      </c>
-      <c r="U67" s="3" t="n">
-        <v>41448</v>
-      </c>
-      <c r="V67" s="3" t="n">
-        <v>41448</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>06/24/2013</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>sTec and WDC</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Joint press release before the market opened announced the signed merger agreement. Balch Hill/Potomac campaign ran until this announcement.</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>“WDC and sTec announced in a joint press release the execution of the merger agreement” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="n"/>
-      <c r="S68" s="2" t="n"/>
-      <c r="T68" s="3" t="n">
+      <c r="T62" s="4" t="n">
         <v>41449</v>
       </c>
-      <c r="U68" s="3" t="n">
+      <c r="U62" s="4" t="n">
         <v>41449</v>
       </c>
-      <c r="V68" s="3" t="n">
+      <c r="V62" s="4" t="n">
         <v>41449</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V68"/>
+  <autoFilter ref="A1:V62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4899,12 +4455,12 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4966,22 +4522,22 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>41365</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch began contacting potential acquirers (18 in all) at the special committee’s direction; IOI process letters 04/23 (WDC, Company D) and 04/26 (Company G).</t>
+          <t>BofA Merrill Lynch began contacting potential acquirers (outreach to 18) after the 03/26/2013 board decision</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>6 strategic entered during the round: Company E (NDA 04/04), Company D (04/10), Company F (04/11), Company G (04/17), WDC (NDA addendum 04/17), Company H (05/08). IOIs were requested from WDC, Company D and Company G; E and F left before any request. Company H: bid still being received, not admitted (no process letter).</t>
+          <t>6 strategic entrants: Company E (04/04), Company D (04/10), Company F (04/11), Company G (04/17), WDC (04/17), Company H (05/08). 0 live at opening.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>05/03/2013 (letters to WDC and D 04/23, to G 04/26; none to H)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -4996,12 +4552,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3 bidders: WDC ($6.60–$7.10, 05/03); Company D (verbal &gt;$5.60 04/23; $5.75 05/10, late); Company H ($5.00–$5.75, 05/15).</t>
+          <t>3: WDC ($6.60–$7.10, 05/03); Company D (&gt;$5.60 oral 04/23; $5.75 written 05/10, late); Company H ($5.00–$5.75, 05/15, no letter)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Two advanced (WDC, Company D). Out during the round: Company F (withdrew 04/24), Company E (dropped late April), Company G (withdrew 05/03). Company H was told its range was insufficient.</t>
+          <t>Two advanced (WDC, Company D); four out (Company F withdrew 04/24; Company E dropped after 04/24; Company G withdrew 05/03; Company H not advanced, dropped 05/23)</t>
         </is>
       </c>
     </row>
@@ -5012,27 +4568,27 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>41410</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>“Final round” process letters with a draft merger agreement sent to WDC and Company D after the 05/16 board meeting.</t>
+          <t>Final-round process letters and draft merger agreement sent to WDC and Company D after the 05/16/2013 board meeting</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: WDC, Company D. Company H still being received, not admitted (invited to submit a revised indication; said 05/23 it could not increase).</t>
+          <t>2 strategic: WDC, Company D. Company H still live until 05/23 but not admitted; no further bid received from it.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>05/28/2013</t>
+          <t>05/28/2013 → 05/30/2013 (best and final)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>Extended; Enforced</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -5042,12 +4598,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1 bidder: WDC ($9.15 cash with merger-agreement markup, 05/28). Company D did not submit and asked for about two weeks.</t>
+          <t>1: WDC ($9.15 with markup, 05/28; orally confirmed as best price 05/30). Company D did not submit.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Board requested best-and-final proposals from both (round 3). Company H out 05/23.</t>
+          <t>WDC selected at $9.15 on 05/30; WDC withdrew 05/31, undoing the selection; Company D still live</t>
         </is>
       </c>
     </row>
@@ -5058,27 +4614,27 @@
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>41423</v>
+      <c r="C4" s="4" t="n">
+        <v>41425</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Board directed BofA to request “best and final” proposals from WDC and Company D by 05/30.</t>
+          <t>Inferred: after WDC withdrew, the target invited Company D to continue (05/31) and held talks with WDC</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: WDC, Company D.</t>
+          <t>2 strategic: Company D (live at opening; withdrew 06/05); WDC (re-entered 06/10)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>05/30/2013</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>No deadline stated</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5088,12 +4644,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1 bidder: WDC ($9.15 confirmed 05/30; after withdrawing 05/31 it returned with $6.60–$7.10 on 06/10 and $6.85 best and final on 06/14). Company D never submitted.</t>
+          <t>1: WDC ($6.60–$7.10, 06/10; $6.85 best and final, 06/14)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Signing with WDC at $6.85 cash (06/23/2013). Company D withdrew 06/05; WDC withdrew 05/31 and re-entered 06/10.</t>
+          <t>Signing with WDC at $6.85, 06/23/2013; Company D had withdrawn 06/05</t>
         </is>
       </c>
     </row>
@@ -5109,16 +4665,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5166,27 +4722,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with three rounds (04/01 outreach; 05/16 “final round” letters; 05/29 best-and-final request)?</t>
+          <t>Should the asset-only expressions of interest (Company C on 03/13 and 04/15; Company F on 04/24; Company E after 04/24; the six asset-only strategics in the 18) be Other-scope bid rows, and should Company E's exit be Withdrew rather than Dropped by target?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Keep one process, rounds 1–3, with WDC’s 06/10 and 06/14 bids and the 06/11 request inside round 3.</t>
+          <t>No Other-scope bid rows: no party proposed terms, a price or a defined asset package; each only said it wanted limited, select assets. Keep Company E as Dropped by target.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gap with no reported acquirer contact: 11/14/2012 (Company A; the meeting cancellation is undated) to 02/13/2013 (Company B), at most ~91 days. E5: (a) met: no offer outstanding; (b) not met: the end was not reported and the undated cancellation means a ~3-month gap is not established; (c) met: special committee 02/13/2013. So one process. Round 1 opens at the 04/01 outreach (pp. 24–27). Round 2: 05/16 letters called “final round” but asked for “non-binding proposals” (p. 30). Round 3: the first best-and-final request (p. 30).</t>
+          <t>The filing reports interest, not proposals: Company C 'expressed a potential interest in exploring an acquisition of particular assets' (p. 26); E and F 'only interested in purchasing limited, select assets' (p. 28). For E, 'the special committee decided not to continue discussions' (p. 28), which is a target decision.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#1, #2, #3, #4, #5, #11, #12, #13, #39, #47, #48, #49, #50, #51, #52, #53, #54, #55, #56, #57, #58, #59, #60, #61, #62, #63, #64, #65, #66</t>
+          <t>#9, #19, #24, #25</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(i) Open round 1 on the 03/26 decision: #11–12 move into round 1. (ii) Fold the 05/29 request into round 2 as bargaining: #47 is dropped, #48–66 become round 2, and round 2’s due dates become 05/28 → 05/30. (iii) Open round 4 on 06/11 for WDC alone: #58–66 move to round 4. (iv) Two processes split at 02/13/2013: #1–5 become process 1, with a Process restarted row at #6.</t>
+          <t>Other-scope bid rows (no price, Informal, Unclear) would be added for C, E, F and a cohort of up to six. E as Withdrew would move one exit from target-driven to bidder-driven; the live count does not change.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5199,27 +4755,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>How do the 18 BofA-contacted prospective acquirers reconcile with the named parties?</t>
+          <t>Process and round map: is this one process with three rounds (R1 opened 04/01/2013; R2 after 05/16/2013; R3 inferred 05/31/2013)?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Remainder cohort of technology companies with Count 12–14, the sponsor on its own row, and B and C kept outside the 18.</t>
+          <t>Yes. One process. R1 = outreach and non-binding indications; R2 = final-round letters to WDC and D (announced final); R3 = the stage after WDC withdrew, ending in signing. Plausible alternatives: R1 opening at the 03/26 board decision (moves nothing but the marker); no R3 (rows #50–#60 move to R2).</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The filing names WDC, H, D, the financial sponsor and Company A as members of the 18 (p. 27). Company B (management contact) and Company C (asset interest) may or may not be among the six asset-only or nine not-interested parties. E, F and G are not placed in any bucket. The 17 other buyers in the reasons section (p. 36) match 18 in total.</t>
+          <t>Gaps of about two months or more with no acquirer contact: 11/14/2012 (Company A contact; the cancellation was sent later, date not given) to 02/13/2013 (Company B), just under three months. E5 tests: (a) met, since nothing was pending with A; (b) not established, as the gap is under three months and no end was reported (the board 'made a determination to continue', p. 24); (c) met by the 02/13 committee. Hence one process. R3 is inferred because the 05/30 selection collapsed when WDC withdrew and the target re-invited D (p. 31).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#7, #8, #9, #14, #15, #19</t>
+          <t>#13, #39, #50</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If B and C are among the 18, the remainder is 12; if neither is, 14. Live-bidder counts are unaffected because none of these parties entered.</t>
+          <t>Without R3, WDC's 06/10 and 06/14 bids would sit in the announced-final R2 and D's exit would be in R2. A process split at 02/13/2013 would put Company A in process 1 only, with no bids there.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -5232,27 +4788,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Round-1 deadline outcome (due 05/03/2013)?</t>
+          <t>How many parties does the residual BofA outreach contact cohort hold, and are Companies B, C, E, F and G members of the stated 18?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted.</t>
+          <t>Count blank, recorded as 'Count: 12–14'. Treat E, F, G and WDC as members; B and C uncertain.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D was given the 05/03 date (p. 28) and said on 05/02 it needed another week. It submitted $5.75 on 05/10, and on 05/15 the target let D continue, conditional on raising its price (p. 29). No extension is reported. WDC met the date and G withdrew on it.</t>
+          <t>'BofA Merrill Lynch had discussions with 18 prospective acquirers, 17 of which were technology companies and one of which was a financial sponsor' (p. 27). WDC, H, D and A are named among the 18. B and C were first contacted by management before BofA was engaged. The reasons section counts '17 other potential buyers' over the whole review (p. 36).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#28, #31, #34, #38</t>
+          <t>#14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>“Extended” if the 05/02 exchange is read as a granted extension. This would not change participation.</t>
+          <t>If B and C are outside the 18, Count = 14; if both are inside, 12. Bidder entries are unaffected, since only NDA signers entered.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -5265,27 +4821,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>How and when did Company H exit?</t>
+          <t>Round 1 deadline outcome for the 05/03/2013 due date.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target on 05/23/2013, Exit reason “Would not improve earlier offer”.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>BofA told H its range was not sufficient to move forward but that a revised indication would be considered. H replied on 05/23 that it could not increase its range (p. 30). H received no final-round letter and had no later contact except repeated statements that it could not raise (p. 34).</t>
+          <t>WDC bid on 05/03 and Company G withdrew that day (p. 29). Company D said on 05/02 that it needed an extra week, submitted in writing on 05/10, was granted data room access on 05/14 and was allowed to continue on 05/15 (p. 29). No extension by the target is reported.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#41, #42</t>
+          <t>#22, #26, #30, #34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing (06/23), which would keep H live through rounds 2–3 (3 live units at round 3 instead of 2). Or Withdrew, though H said it “remained interested”.</t>
+          <t>If D's 04/23 oral indication counts as its round-1 response, the outcome would be Enforced and #34 a revision of #23. The due-date list is unchanged.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -5298,27 +4854,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Round-2 deadline outcome (due 05/28/2013)?</t>
+          <t>Company H's exit: Dropped by target with 'Would not improve earlier offer', or Withdrew with 'Lower offer than rivals'?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Enforced.</t>
+          <t>Dropped by target, Would not improve earlier offer, dated 05/23/2013.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>On 05/29 the board acted on the bid in hand, WDC’s $9.15 with its markup: it opened a best-and-final request with a 05/30 due date (p. 30). D, which had not submitted, was still invited.</t>
+          <t>The target told H its range 'was not sufficient to move them forward in the process' but invited a revision (p. 30). H then said it 'was not able to increase its indicated value range' while remaining interested (p. 30), and got no final-round letter. The convention gives Would not improve earlier offer to a bidder asked to improve that declines.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#45, #46</t>
+          <t>#41, #42</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If the 05/29 request is folded into round 2 (see the map Question), the outcome becomes “Extended” with due dates 05/28 → 05/30, and round 2 ends with the board’s 05/30 decision.</t>
+          <t>Withdrew would make the exit bidder-driven. Dating the exit to round-2 opening (after 05/16) would drop H before its 05/23 reply.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -5331,27 +4887,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Should Company D’s non-submissions on 05/28 and 05/30 be exits (Did not submit), with Re-entered rows?</t>
+          <t>Conditions on WDC's 05/28 ($9.15) and 06/14 ($6.85) bids: Light, or Unclear?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>No: record them as events within the round and a single Withdrew exit on 06/05/2013.</t>
+          <t>Light for both.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Each time, D asked for more time, said it would move meaningfully on value or be competitive, and the target kept inviting it (05/31 call; 06/01 data-room postings). Its participation looks continuous until it disengaged on 06/05 (pp. 30–32).</t>
+          <t>Each bid gave a short signing or announcement horizon: 'signing definitive documentation ... by no later than June 3' (p. 30) and 'in a position to announce a transaction on June 24' (p. 32). That means expedited diligence only; the later diligence was described as 'confirmatory' (p. 33). No financing condition is reported, and the merger agreement has none (p. 36).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#45, #49, #53, #55</t>
+          <t>#44, #55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Add Did not submit rows at 05/28 and 05/30 and Re-entered rows at 05/29 and 05/31. D would then not be live at the round-3 opening, WDC would be the sole round-3 invitee at times, and D’s exit reason on 06/05 would remain.</t>
+          <t>Unclear on either row would weaken the evidence that WDC's winning offers were near-unconditional. Formality is unaffected.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -5364,27 +4920,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WDC’s 05/31 pull-back and 06/10 return: an exit and re-entry? And how should the 05/30 and 06/10 bids be classified?</t>
+          <t>Round 2 deadline outcomes (05/28 and 05/30/2013), and should Company D get a Did not submit exit?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Withdrew on 05/31 (“at that time”) and Re-entered on 06/10. The 05/30 confirmation is a round-3 Bid (Formal). The 06/10 range is Formal with Conditions Unclear.</t>
+          <t>Outcomes: Extended; Enforced. No Did not submit row for Company D; its single exit is Withdrew on 06/05/2013.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>WDC said it was not prepared to proceed and stopped diligence, then returned with a lower written range “otherwise prepared” to proceed on its 05/28 terms, including the markup (pp. 31–32). The 05/30 statement answered a best-and-final request.</t>
+          <t>On 05/29 the board requested best-and-final proposals by 05/30 (p. 30), which extends 05/28. On 05/30 the board decided to proceed with WDC on the bid in hand (p. 31), which enforces 05/30. D missed both dates but kept saying it was interested (pp. 30–31). The target re-invited D on 05/31 (p. 31), and D disengaged on 06/05 (p. 32).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#48, #52, #56, #57</t>
+          <t>#45, #46, #47, #51</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Treat WDC as continuously live, with no exit or re-entry. Or mark the 06/10 range Informal, since it was a range the board refused to consider, which lowers the formal-bid count. Or treat 05/30 as no new bid, which leaves round 3 without a pre-withdrawal bid.</t>
+          <t>A Did not submit exit on 05/30 would need an inferred Re-entered row on 05/31. D's live period would break, leaving WDC alone in R2 at the 05/30 decision.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -5397,33 +4953,66 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Round-3 deadline outcome (due 05/30/2013)?</t>
+          <t>Was WDC's 05/31 message a withdrawal followed by re-entry on 06/10, or continued participation?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Enforced.</t>
+          <t>Withdrew (for now) on 05/31, then Re-entered on 06/10.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>On 05/30, with WDC confirming $9.15 and D asking for more time, the board decided to proceed with WDC and told WDC so (p. 31). After WDC pulled back on 05/31, D was re-invited without a new due date and no further due date was set.</t>
+          <t>WDC was 'not prepared to move forward with a transaction with sTec at that time' and 'discontinued their due diligence efforts' (p. 31). From 06/01 to 06/10 it was 'reconsidering their interest' (p. 32) and made no offer until 06/10.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#49, #50, #51</t>
+          <t>#49, #50, #52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>“Passed without action” if the later re-invitation of D is read as bidding simply continuing. This would not change live-bidder counts.</t>
+          <t>Without the exit and re-entry, WDC would be live throughout and R3 would be harder to justify as a new stage. The 06/10 bid would read as a revision within R2.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Is WDC's 06/10 range bid ($6.60–$7.10) Formal or Informal?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Formal, with Conditions Unclear.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>WDC said it 'was otherwise prepared to move forward on the transaction terms previously proposed on May 28, 2013' (p. 32), and those terms included its merger agreement markup (p. 30). A range does not change the label (E11), although the filing calls the bid a 'revised written indication of interest'.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>#53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Informal would treat WDC's price cut from $9.15 as an informal re-indication before its formal $6.85 offer.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5437,7 +5026,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -5473,7 +5062,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Western Digital Corporation (WDC), through Lodi Ventures, Inc., its wholly owned merger subsidiary</t>
+          <t>Western Digital Corporation (WDC), through its wholly-owned subsidiary Lodi Ventures, Inc. (merger sub)</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5074,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (storage-products manufacturer: WD, HGST and G-Technology brands)</t>
+          <t>Strategic (storage-products developer and manufacturer; WD, HGST and G-Technology brands)</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5086,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$6.85 per share in cash, without interest; no financing condition. Termination fees: $9.4 million payable by sTec, $17.0 million reverse fee payable by WDC.</t>
+          <t>$6.85 per share in cash, without interest; no financing condition; options and RSUs assumed and converted into WDC awards; $9.4 million target termination fee</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5110,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>06/24/2013 (joint press release before the market opened)</t>
+          <t>06/24/2013 (joint press release before market open)</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5122,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A (definitive proxy statement) dated 08/07/2013; supplied file dated 2013-08-08</t>
+          <t>DEFM14A (definitive proxy statement) dated 08/07/2013; EDGAR filing date 08/08/2013 per supplied file</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5146,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Target-led. In mid-November 2012 the board decided on a formal review of strategic alternatives including a sale. Activist pressure (Balch Hill 13D 11/16/2012, letter 12/06/2012) came alongside it. Company A, B, C and D approaches preceded the organised outreach.</t>
+          <t>target-led: the board decided on a market check in mid-November 2012 and ran the 04/01/2013 outreach; activist Balch Hill/Potomac pressed for strategic alternatives from 12/06/2012; Company A (11/2012), B, C, D and H approached on their own</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5170,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2011: at an industry event, WDC’s then CEO told Manouch Moshayedi that WDC wanted to expand in SSDs. Summer 2012: WDC’s Michael Hajeck asked whether the Moshayedis planned to retire. Neither led to further discussion. Other informal third-party approaches were “general and exploratory”, with no terms proposed (pp. 23–24).</t>
+          <t>Undated informal approaches from third parties over the years, 'general and exploratory' with no terms proposed; a 2011 lunch where WDC's then CEO John Coyne said WDC wanted to expand in SSDs; a summer 2012 lunch where WDC's Michael Hajeck asked about the Moshayedis' retirement plans. No further WDC discussion until the process (pp. 23–24).</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5182,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 6 parties (WDC by NDA addendum; Companies D, E, F, G, H)</t>
+          <t>Met (process 1): 6 parties (Company E, Company D, Company F, Company G, Company H, and WDC through an addendum to its 01/29/2009 NDA)</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5194,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (asset-only interest from Company C, Company E, Company F and six strategics overall produced no proposals)</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5206,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share</t>
+          <t>US dollars per share; all bids per share</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5218,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BofA Merrill Lynch</t>
+          <t>BofA Merrill Lynch (Merrill Lynch, Pierce, Fenner &amp; Smith Incorporated), approved 03/26/2013, engagement letter 03/28/2013</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5230,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Gibson, Dunn &amp; Crutcher LLP (corporate counsel); Latham &amp; Watkins LLP (litigation counsel to sTec and Manouch Moshayedi)</t>
+          <t>Gibson, Dunn &amp; Crutcher LLP (outside corporate counsel); Latham &amp; Watkins LLP (litigation counsel to sTec and Manouch Moshayedi)</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5242,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Facing losses and activist pressure, sTec’s board began a review including a sale in late 2012, formed a special committee in February 2013 and hired BofA Merrill Lynch in March. From 04/01/2013, BofA contacted 18 prospective acquirers, six signed NDAs, and WDC, Company D and Company H made indications from $5.00 to $7.10. WDC and D advanced to a final round, where WDC bid $9.15 with a merger-agreement markup while D kept asking for more time. After the board chose WDC at $9.15, WDC pulled back on 05/31, D disengaged on 06/05, and WDC returned at $6.60–$7.10 and then $6.85 best and final. The board accepted, and the merger agreement was signed on 06/23/2013 and announced on 06/24/2013.</t>
+          <t>As losses mounted and activist Balch Hill pressed for change, sTec's board decided in late 2012 to test a sale, set up a special committee on 02/13/2013 and hired BofA Merrill Lynch in late March. From 04/01/2013 BofA contacted 18 prospective acquirers; six signed NDAs, most interested parties wanted only select assets, and WDC, Company D and Company H gave non-binding indications of $6.60–$7.10, $5.75 and $5.00–$5.75. WDC and Company D were invited to a final round; WDC bid $9.15 with a merger agreement markup and confirmed it as best and final, while Company D kept asking for more time. The board chose WDC on 05/30, but WDC withdrew the next day, and Company D disengaged on 06/05. WDC came back at $6.60–$7.10, was told to name one best price, offered $6.85 on 06/14, and signed on 06/23/2013; the deal was announced on 06/24.</t>
         </is>
       </c>
     </row>
